--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G2" t="n">
         <v>3.1</v>
@@ -769,7 +769,7 @@
         <v>2.84</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="I4" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="J4" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>2.62</v>
       </c>
       <c r="G5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
         <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
         <v>2.9</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
         <v>3.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
         <v>3.15</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -766,13 +766,13 @@
         <v>2.58</v>
       </c>
       <c r="I2" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>2.62</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H5" t="n">
         <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J5" t="n">
         <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
         <v>2.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Australian A-League Men</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>05:35:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Adelaide United</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.76</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>2.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>2.92</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Le Puy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5</v>
+        <v>1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.14</v>
+        <v>6.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Le Puy</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,201 +1502,395 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Rapid Bucharest</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-18 07:32:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>America de Cali S.A</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>2.96</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="G7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H7" t="n">
         <v>2.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>3.15</v>
       </c>
-      <c r="J6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="J7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.45</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-03-18 05:22:48</t>
+      <c r="Q7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -790,7 +790,7 @@
         <v>2.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.75</v>
@@ -805,7 +805,7 @@
         <v>2.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
         <v>2.04</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 07:32:39</t>
+          <t>2026-03-18 09:42:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Shanghai Port FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.64</v>
+        <v>1.99</v>
       </c>
       <c r="I3" t="n">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 07:32:39</t>
+          <t>2026-03-18 09:42:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Zhejiang Greentown</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.49</v>
+        <v>4.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>6.4</v>
+        <v>1.87</v>
       </c>
       <c r="I4" t="n">
-        <v>8.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N4" t="n">
         <v>5.1</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 07:32:39</t>
+          <t>2026-03-18 09:42:52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Le Puy</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="H5" t="n">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="I5" t="n">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 07:32:39</t>
+          <t>2026-03-18 09:42:52</t>
         </is>
       </c>
     </row>
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.56</v>
+        <v>1.49</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,201 +1696,589 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 07:32:39</t>
+          <t>2026-03-18 09:42:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Villefranche Beaujolais</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Le Puy</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-18 09:42:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rapid Bucharest</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-18 09:42:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>America de Cali S.A</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F9" t="n">
         <v>2.96</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G9" t="n">
         <v>3.85</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H9" t="n">
         <v>2.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I9" t="n">
         <v>3.15</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J9" t="n">
         <v>2.76</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K9" t="n">
         <v>3.45</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q9" t="n">
         <v>2.14</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-03-18 07:32:39</t>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-18 09:42:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -760,10 +760,10 @@
         <v>1.94</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
         <v>3.95</v>
@@ -802,13 +802,13 @@
         <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X2" t="n">
         <v>38</v>
@@ -826,7 +826,7 @@
         <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
         <v>17.5</v>
@@ -850,7 +850,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -862,19 +862,19 @@
         <v>7.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
         <v>26</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
@@ -886,7 +886,7 @@
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -898,7 +898,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
         <v>6.4</v>
@@ -910,7 +910,7 @@
         <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
@@ -1008,13 +1008,13 @@
         <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
         <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AB3" t="n">
         <v>26</v>
@@ -1023,7 +1023,7 @@
         <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>21</v>
@@ -1032,7 +1032,7 @@
         <v>36</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
         <v>17</v>
@@ -1053,7 +1053,7 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="n">
         <v>9.800000000000001</v>
@@ -1095,16 +1095,16 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>48</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>4.2</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I4" t="n">
         <v>2.02</v>
@@ -1163,7 +1163,7 @@
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1190,16 +1190,16 @@
         <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.98</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>13</v>
@@ -1211,10 +1211,10 @@
         <v>23</v>
       </c>
       <c r="AB4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>10.5</v>
@@ -1238,10 +1238,10 @@
         <v>100</v>
       </c>
       <c r="AK4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL4" t="n">
         <v>55</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>80</v>
@@ -1256,25 +1256,25 @@
         <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
         <v>16.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AX4" t="n">
         <v>30</v>
@@ -1283,22 +1283,22 @@
         <v>15</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
         <v>23</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
         <v>36</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
         <v>25</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="H5" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>6.4</v>
       </c>
       <c r="I6" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
         <v>4.2</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
         <v>3.5</v>
@@ -1954,7 +1954,7 @@
         <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G9" t="n">
         <v>3.85</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
         <v>1.5</v>
@@ -802,7 +802,7 @@
         <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
@@ -868,10 +868,10 @@
         <v>26</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS2" t="n">
         <v>7.8</v>
@@ -886,7 +886,7 @@
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -898,7 +898,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
         <v>6.4</v>
@@ -910,7 +910,7 @@
         <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -1011,13 +1011,13 @@
         <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC3" t="n">
         <v>13</v>
@@ -1095,16 +1095,16 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>48</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J4" t="n">
         <v>3.7</v>
@@ -1187,16 +1187,16 @@
         <v>2.46</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U4" t="n">
         <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1208,7 +1208,7 @@
         <v>14.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB4" t="n">
         <v>23</v>
@@ -1226,7 +1226,7 @@
         <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH4" t="n">
         <v>17</v>
@@ -1238,10 +1238,10 @@
         <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
         <v>80</v>
@@ -1256,7 +1256,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1280,7 +1280,7 @@
         <v>30</v>
       </c>
       <c r="AY4" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>13.5</v>
@@ -1295,27 +1295,27 @@
         <v>36</v>
       </c>
       <c r="BD4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
         <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG4" t="n">
         <v>8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.49</v>
+        <v>2.54</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Le Puy</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J7" t="n">
         <v>2.44</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>1.45</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,378 +1907,1154 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UTA Arad</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-18 14:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-18 14:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Villefranche Beaujolais</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Le Puy</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-18 14:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rapid Bucharest</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-18 14:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>America de Cali S.A</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G13" t="n">
         <v>3.85</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H13" t="n">
         <v>2.5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I13" t="n">
         <v>3.15</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J13" t="n">
         <v>2.76</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K13" t="n">
         <v>3.45</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q13" t="n">
         <v>2.14</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-03-18 11:52:45</t>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BH49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,7 +790,7 @@
         <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R2" t="n">
         <v>1.75</v>
@@ -865,13 +865,13 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
         <v>7.8</v>
@@ -886,7 +886,7 @@
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -898,7 +898,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
         <v>6.4</v>
@@ -907,10 +907,10 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>1.71</v>
       </c>
       <c r="S3" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T3" t="n">
         <v>1.48</v>
@@ -1059,7 +1059,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>14</v>
@@ -1068,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>19</v>
@@ -1083,7 +1083,7 @@
         <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="AY3" t="n">
         <v>13.5</v>
@@ -1095,7 +1095,7 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>48</v>
+        <v>5.7</v>
       </c>
       <c r="BC3" t="n">
         <v>5.3</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H4" t="n">
         <v>1.89</v>
@@ -1157,7 +1157,7 @@
         <v>2.04</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
@@ -1166,7 +1166,7 @@
         <v>1.26</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>5.1</v>
@@ -1190,13 +1190,13 @@
         <v>1.56</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1238,10 +1238,10 @@
         <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
         <v>80</v>
@@ -1253,10 +1253,10 @@
         <v>9.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1280,7 +1280,7 @@
         <v>30</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>13.5</v>
@@ -1292,7 +1292,7 @@
         <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1301,14 +1301,14 @@
         <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
         <v>3.5</v>
@@ -1405,22 +1405,22 @@
         <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
         <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>34</v>
@@ -1453,10 +1453,10 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1465,44 +1465,44 @@
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF5" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
         <v>2.78</v>
@@ -1548,7 +1548,7 @@
         <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.32</v>
@@ -1575,7 +1575,7 @@
         <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
         <v>2.22</v>
@@ -1677,13 +1677,13 @@
         <v>8.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
         <v>9.800000000000001</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
         <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J7" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="L7" t="n">
         <v>1.4</v>
@@ -1754,19 +1754,19 @@
         <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7" t="n">
         <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G8" t="n">
         <v>6.6</v>
@@ -1930,13 +1930,13 @@
         <v>1.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,34 +1945,34 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
         <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,69 +2029,69 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.6</v>
+        <v>3.55</v>
       </c>
       <c r="AW8" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>32</v>
+        <v>4.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>50</v>
+        <v>4.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>40</v>
+        <v>4.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>40</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>44</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Slovan Bratislava II</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
-        <v>1.61</v>
+        <v>500</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>1.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="H10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
         <v>4.2</v>
       </c>
-      <c r="I10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.82</v>
-      </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Znicz Pruszkow</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Le Puy</t>
+          <t>Stal Rzeszow</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
-        <v>2.14</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>3.65</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,378 +2683,7362 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="G12" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Riteriai</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fk Siauliai</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K13" t="n">
+        <v>950</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cypriot 1st Division</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Omonia FC Aradippou</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Enosis Neon Paralimni</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>55</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>110</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Austria Klagenfurt</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>First Vienna Fc 1894</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>German Bundesliga 2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X16" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>German Bundesliga 2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>260</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>250</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>95</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Danish Superliga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wehen Wiesbaden</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Portuguese Segunda Liga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Leiria</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Villefranche Beaujolais</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Le Puy</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Swiss Challenge League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bellinzona</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Stade Lausanne-Ouchy</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Austrian Bundesliga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sturm Graz</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Red Bull Salzburg</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>French Ligue 2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Boulogne</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hungarian NB I</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MTK Budapest</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Paks</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>French Ligue 2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>French Ligue 2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>French Ligue 2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>French Ligue 2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dutch Eredivisie</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Heracles</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>French Ligue 2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Le Mans</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X33" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dutch Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Cambuur Leeuwarden</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Jong AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X34" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dutch Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jong Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dutch Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Roda JC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Helmond Sport</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dutch Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jong PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Vitesse Arnhem</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>27</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dutch Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>VVV Venlo</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X38" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dutch Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FC Dordrecht</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dutch Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FC Oss</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FC Eindhoven</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X40" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Swiss Challenge League</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>FC Vaduz</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Yverdon Sport</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X41" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LKP Motor Lublin</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Zaglebie Lubin</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>German Bundesliga</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ternana</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sambenedettese</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sassari Torres</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Rapid Bucharest</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>America de Cali S.A</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F49" t="n">
         <v>2.96</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G49" t="n">
         <v>3.85</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H49" t="n">
         <v>2.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I49" t="n">
         <v>3.15</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J49" t="n">
         <v>2.76</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K49" t="n">
         <v>3.45</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q49" t="n">
         <v>2.14</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-03-18 14:02:38</t>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -787,10 +787,10 @@
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
         <v>1.75</v>
@@ -805,64 +805,64 @@
         <v>2.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X2" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z2" t="n">
         <v>36</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>42</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
         <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN2" t="n">
         <v>7.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
         <v>24</v>
@@ -871,13 +871,13 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
         <v>9.6</v>
@@ -886,7 +886,7 @@
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -898,29 +898,29 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -987,10 +987,10 @@
         <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
         <v>1.48</v>
@@ -1002,7 +1002,7 @@
         <v>1.89</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
@@ -1068,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
         <v>19</v>
@@ -1083,7 +1083,7 @@
         <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY3" t="n">
         <v>13.5</v>
@@ -1095,13 +1095,13 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC3" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
         <v>5.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1157,13 +1157,13 @@
         <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>10.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1175,7 +1175,7 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
         <v>1.71</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.3</v>
@@ -1363,7 +1363,7 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
@@ -1372,22 +1372,22 @@
         <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
         <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U5" t="n">
         <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.27</v>
@@ -1405,7 +1405,7 @@
         <v>24</v>
       </c>
       <c r="AB5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC5" t="n">
         <v>9</v>
@@ -1417,13 +1417,13 @@
         <v>17.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>28</v>
@@ -1447,7 +1447,7 @@
         <v>9.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>11</v>
@@ -1489,7 +1489,7 @@
         <v>26</v>
       </c>
       <c r="BD5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE5" t="n">
         <v>29</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="K6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,31 +1557,31 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
         <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
         <v>2.48</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -1641,52 +1641,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
         <v>3.2</v>
@@ -1784,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>25</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>19.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1975,58 +1975,58 @@
         <v>1.57</v>
       </c>
       <c r="X8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD8" t="n">
         <v>16</v>
       </c>
-      <c r="Y8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AE8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
         <v>46</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>40</v>
       </c>
       <c r="AM8" t="n">
         <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AP8" t="n">
         <v>13</v>
@@ -2035,10 +2035,10 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2062,19 +2062,19 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.8</v>
+        <v>3.85</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BF8" t="n">
         <v>19</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
         <v>4.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
         <v>1.54</v>
@@ -2357,7 +2357,7 @@
         <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="W10" t="n">
         <v>1.18</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
@@ -2533,7 +2533,7 @@
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
         <v>2.1</v>
@@ -2551,7 +2551,7 @@
         <v>1.91</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W11" t="n">
         <v>1.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>1.16</v>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I12" t="n">
         <v>60</v>
@@ -2712,7 +2712,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.24</v>
@@ -2820,7 +2820,7 @@
         <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV12" t="n">
         <v>6.6</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2918,19 +2918,19 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G14" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J14" t="n">
         <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3115,16 +3115,16 @@
         <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="R14" t="n">
         <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T14" t="n">
         <v>1.81</v>
@@ -3133,10 +3133,10 @@
         <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
         <v>15</v>
@@ -3157,7 +3157,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
@@ -3193,10 +3193,10 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AR14" t="n">
         <v>17.5</v>
@@ -3205,7 +3205,7 @@
         <v>4.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="AU14" t="n">
         <v>5.8</v>
@@ -3214,31 +3214,31 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.4</v>
+        <v>3.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
       </c>
       <c r="BB14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC14" t="n">
         <v>3.85</v>
       </c>
-      <c r="BC14" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
         <v>16.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3306,13 +3306,13 @@
         <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
         <v>1.49</v>
@@ -3327,10 +3327,10 @@
         <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.52</v>
       </c>
       <c r="G16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="n">
         <v>6.4</v>
@@ -3485,7 +3485,7 @@
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K16" t="n">
         <v>5.1</v>
@@ -3524,7 +3524,7 @@
         <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X16" t="n">
         <v>20</v>
@@ -3539,19 +3539,19 @@
         <v>240</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
         <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE16" t="n">
         <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
@@ -3587,10 +3587,10 @@
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT16" t="n">
         <v>7.6</v>
@@ -3599,10 +3599,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
         <v>8.199999999999999</v>
@@ -3614,7 +3614,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
         <v>12</v>
@@ -3623,20 +3623,20 @@
         <v>13.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BF16" t="n">
         <v>6</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
         <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P18" t="n">
         <v>1.66</v>
@@ -3927,7 +3927,7 @@
         <v>16</v>
       </c>
       <c r="AB18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G19" t="n">
         <v>1.59</v>
@@ -4094,10 +4094,10 @@
         <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T19" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
         <v>2.18</v>
@@ -4109,49 +4109,49 @@
         <v>2.68</v>
       </c>
       <c r="X19" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
         <v>28</v>
       </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA19" t="n">
         <v>170</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
         <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>70</v>
       </c>
       <c r="AJ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK19" t="n">
         <v>15.5</v>
       </c>
-      <c r="AK19" t="n">
-        <v>17</v>
-      </c>
       <c r="AL19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM19" t="n">
         <v>90</v>
@@ -4169,10 +4169,10 @@
         <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX19" t="n">
         <v>9.800000000000001</v>
@@ -4196,7 +4196,7 @@
         <v>17.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
         <v>13</v>
@@ -4208,17 +4208,17 @@
         <v>24</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BF19" t="n">
         <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>60</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G20" t="n">
         <v>2.22</v>
@@ -4258,7 +4258,7 @@
         <v>3.4</v>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>3.85</v>
@@ -4321,7 +4321,7 @@
         <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>38</v>
@@ -4339,13 +4339,13 @@
         <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
         <v>70</v>
@@ -4390,7 +4390,7 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB20" t="n">
         <v>21</v>
@@ -4402,7 +4402,7 @@
         <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>40</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
         <v>8.199999999999999</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G22" t="n">
         <v>2.66</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>6.2</v>
@@ -4652,7 +4652,7 @@
         <v>2.16</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q22" t="n">
         <v>2.76</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H25" t="n">
         <v>2.24</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>2.14</v>
       </c>
       <c r="I26" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="J26" t="n">
         <v>3.1</v>
@@ -5446,7 +5446,7 @@
         <v>1.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
@@ -5455,10 +5455,10 @@
         <v>3.85</v>
       </c>
       <c r="T26" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
@@ -5530,7 +5530,7 @@
         <v>10.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT26" t="n">
         <v>9.199999999999999</v>
@@ -5554,29 +5554,29 @@
         <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF26" t="n">
-        <v>48</v>
+        <v>4.8</v>
       </c>
       <c r="BG26" t="n">
         <v>18.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5610,19 @@
         <v>3.6</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="I27" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5631,34 +5631,34 @@
         <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="O27" t="n">
         <v>1.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>2.78</v>
       </c>
       <c r="G29" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H29" t="n">
         <v>2.2</v>
@@ -6007,7 +6007,7 @@
         <v>2.48</v>
       </c>
       <c r="J29" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
         <v>4.6</v>
@@ -6034,7 +6034,7 @@
         <v>1.74</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
         <v>1.45</v>
@@ -6043,46 +6043,46 @@
         <v>2.74</v>
       </c>
       <c r="V29" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X29" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Y29" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC29" t="n">
         <v>13</v>
       </c>
       <c r="AD29" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
       </c>
       <c r="AF29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AG29" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH29" t="n">
         <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AJ29" t="n">
         <v>1000</v>
@@ -6091,7 +6091,7 @@
         <v>32</v>
       </c>
       <c r="AL29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT29" t="n">
         <v>15.5</v>
       </c>
       <c r="AU29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX29" t="n">
         <v>4.3</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AY29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA29" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BB29" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BF29" t="n">
         <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>3.35</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G32" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H32" t="n">
         <v>3.25</v>
@@ -6592,7 +6592,7 @@
         <v>3.05</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6601,13 +6601,13 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
         <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q32" t="n">
         <v>2.24</v>
@@ -6619,13 +6619,13 @@
         <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U32" t="n">
         <v>1.9</v>
       </c>
       <c r="V32" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W32" t="n">
         <v>1.64</v>
@@ -6658,7 +6658,7 @@
         <v>17.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH32" t="n">
         <v>23</v>
@@ -6676,7 +6676,7 @@
         <v>60</v>
       </c>
       <c r="AM32" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN32" t="n">
         <v>30</v>
@@ -6694,7 +6694,7 @@
         <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT32" t="n">
         <v>7.4</v>
@@ -6706,7 +6706,7 @@
         <v>12.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX32" t="n">
         <v>12.5</v>
@@ -6718,29 +6718,29 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD32" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
         <v>17</v>
       </c>
       <c r="AG34" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH34" t="n">
         <v>23</v>
@@ -7067,7 +7067,7 @@
         <v>190</v>
       </c>
       <c r="AN34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO34" t="n">
         <v>85</v>
@@ -7082,7 +7082,7 @@
         <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT34" t="n">
         <v>6.8</v>
@@ -7094,7 +7094,7 @@
         <v>13.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX34" t="n">
         <v>12.5</v>
@@ -7109,26 +7109,26 @@
         <v>55</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD34" t="n">
         <v>44</v>
       </c>
       <c r="BE34" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
         <v>1.92</v>
       </c>
       <c r="T35" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U35" t="n">
         <v>2.58</v>
@@ -7210,7 +7210,7 @@
         <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X35" t="n">
         <v>48</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
         <v>27</v>
       </c>
       <c r="Y36" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z36" t="n">
         <v>22</v>
@@ -7422,10 +7422,10 @@
         <v>20</v>
       </c>
       <c r="AC36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD36" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE36" t="n">
         <v>28</v>
@@ -7434,7 +7434,7 @@
         <v>29</v>
       </c>
       <c r="AG36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH36" t="n">
         <v>18.5</v>
@@ -7452,16 +7452,16 @@
         <v>42</v>
       </c>
       <c r="AM36" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN36" t="n">
         <v>25</v>
       </c>
       <c r="AO36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AQ36" t="n">
         <v>10.5</v>
@@ -7470,7 +7470,7 @@
         <v>15.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AT36" t="n">
         <v>12</v>
@@ -7482,7 +7482,7 @@
         <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AX36" t="n">
         <v>20</v>
@@ -7497,16 +7497,16 @@
         <v>21</v>
       </c>
       <c r="BB36" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BC36" t="n">
         <v>21</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.1</v>
+        <v>42</v>
       </c>
       <c r="BF36" t="n">
         <v>14.5</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
         <v>9</v>
       </c>
       <c r="BB37" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BC37" t="n">
         <v>8.199999999999999</v>
@@ -7700,7 +7700,7 @@
         <v>9</v>
       </c>
       <c r="BE37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="BF37" t="n">
         <v>13</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
         <v>1.77</v>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="J38" t="n">
         <v>4.5</v>
@@ -7774,7 +7774,7 @@
         <v>3.35</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="R38" t="n">
         <v>1.96</v>
@@ -7789,10 +7789,10 @@
         <v>2.96</v>
       </c>
       <c r="V38" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X38" t="n">
         <v>55</v>
@@ -7852,22 +7852,22 @@
         <v>3.95</v>
       </c>
       <c r="AQ38" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR38" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AS38" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>22</v>
+        <v>3.8</v>
       </c>
       <c r="AU38" t="n">
         <v>9.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW38" t="n">
         <v>12</v>
@@ -7876,7 +7876,7 @@
         <v>3.9</v>
       </c>
       <c r="AY38" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AZ38" t="n">
         <v>11</v>
@@ -7885,7 +7885,7 @@
         <v>15.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="BC38" t="n">
         <v>3.9</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>1.63</v>
       </c>
       <c r="G39" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H39" t="n">
         <v>4.7</v>
@@ -7986,7 +7986,7 @@
         <v>1.18</v>
       </c>
       <c r="W39" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -8132,16 +8132,16 @@
         <v>2.86</v>
       </c>
       <c r="G40" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H40" t="n">
         <v>2.22</v>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K40" t="n">
         <v>4.6</v>
@@ -8177,7 +8177,7 @@
         <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W40" t="n">
         <v>1.4</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -8326,16 +8326,16 @@
         <v>1.92</v>
       </c>
       <c r="G41" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="H41" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I41" t="n">
         <v>3.9</v>
       </c>
       <c r="J41" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
         <v>4.8</v>
@@ -8365,7 +8365,7 @@
         <v>2.16</v>
       </c>
       <c r="T41" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U41" t="n">
         <v>2.62</v>
@@ -8374,7 +8374,7 @@
         <v>1.35</v>
       </c>
       <c r="W41" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="X41" t="n">
         <v>36</v>
@@ -8431,7 +8431,7 @@
         <v>25</v>
       </c>
       <c r="AP41" t="n">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="AQ41" t="n">
         <v>17</v>
@@ -8446,7 +8446,7 @@
         <v>12</v>
       </c>
       <c r="AU41" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV41" t="n">
         <v>12</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -8520,16 +8520,16 @@
         <v>2.48</v>
       </c>
       <c r="G42" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="H42" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="J42" t="n">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="K42" t="n">
         <v>4.4</v>
@@ -8565,10 +8565,10 @@
         <v>2.58</v>
       </c>
       <c r="V42" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W42" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X42" t="n">
         <v>34</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -8714,13 +8714,13 @@
         <v>1.89</v>
       </c>
       <c r="G43" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H43" t="n">
         <v>3.8</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
         <v>3.7</v>
@@ -8750,16 +8750,16 @@
         <v>1.42</v>
       </c>
       <c r="S43" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="T43" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U43" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
         <v>1.92</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
         <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
         <v>1.3</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
         <v>1.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R45" t="n">
         <v>1.37</v>
@@ -9147,7 +9147,7 @@
         <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W45" t="n">
         <v>1.78</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
         <v>34</v>
       </c>
       <c r="Y46" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z46" t="n">
         <v>36</v>
@@ -9362,7 +9362,7 @@
         <v>19</v>
       </c>
       <c r="AC46" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD46" t="n">
         <v>16</v>
@@ -9449,14 +9449,14 @@
         <v>36</v>
       </c>
       <c r="BF46" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG46" t="n">
         <v>16.5</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
         <v>4.9</v>
       </c>
       <c r="J48" t="n">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="K48" t="n">
         <v>4.4</v>
@@ -9729,7 +9729,7 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W48" t="n">
         <v>1.53</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="H49" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J49" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K49" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9905,76 +9905,76 @@
         <v>1.41</v>
       </c>
       <c r="P49" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R49" t="n">
         <v>1.28</v>
       </c>
       <c r="S49" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="T49" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U49" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W49" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X49" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Y49" t="n">
         <v>13</v>
       </c>
       <c r="Z49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA49" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB49" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD49" t="n">
         <v>17</v>
       </c>
       <c r="AE49" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF49" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI49" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ49" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AK49" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL49" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM49" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN49" t="n">
         <v>36</v>
@@ -9983,62 +9983,62 @@
         <v>55</v>
       </c>
       <c r="AP49" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ49" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT49" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU49" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV49" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="AX49" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY49" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ49" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA49" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE49" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB49" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -10072,16 +10072,16 @@
         <v>3.2</v>
       </c>
       <c r="G50" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="H50" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I50" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="J50" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K50" t="n">
         <v>3.8</v>
@@ -10117,10 +10117,10 @@
         <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W50" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X50" t="n">
         <v>970</v>
@@ -10135,13 +10135,13 @@
         <v>34</v>
       </c>
       <c r="AB50" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC50" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD50" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE50" t="n">
         <v>27</v>
@@ -10156,22 +10156,22 @@
         <v>970</v>
       </c>
       <c r="AI50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ50" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL50" t="n">
         <v>60</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>50</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AO50" t="n">
         <v>21</v>
@@ -10186,7 +10186,7 @@
         <v>12</v>
       </c>
       <c r="AS50" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT50" t="n">
         <v>10</v>
@@ -10198,10 +10198,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW50" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="AX50" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AY50" t="n">
         <v>11</v>
@@ -10210,29 +10210,29 @@
         <v>13</v>
       </c>
       <c r="BA50" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB50" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BC50" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD50" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BE50" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF50" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BG50" t="n">
         <v>15</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.2</v>
       </c>
       <c r="G51" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H51" t="n">
         <v>8.6</v>
@@ -10275,7 +10275,7 @@
         <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K51" t="n">
         <v>19.5</v>
@@ -10287,19 +10287,19 @@
         <v>1.02</v>
       </c>
       <c r="N51" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O51" t="n">
         <v>1.13</v>
       </c>
       <c r="P51" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R51" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S51" t="n">
         <v>1.94</v>
@@ -10314,7 +10314,7 @@
         <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G52" t="n">
         <v>2.32</v>
@@ -10565,7 +10565,7 @@
         <v>95</v>
       </c>
       <c r="AP52" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ52" t="n">
         <v>9.800000000000001</v>
@@ -10586,7 +10586,7 @@
         <v>15.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AX52" t="n">
         <v>11.5</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -10678,13 +10678,13 @@
         <v>1.25</v>
       </c>
       <c r="O53" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="P53" t="n">
         <v>1.24</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="R53" t="n">
         <v>1.2</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -10845,16 +10845,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G54" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H54" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>3.95</v>
@@ -10872,13 +10872,13 @@
         <v>3.6</v>
       </c>
       <c r="O54" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P54" t="n">
         <v>1.89</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="R54" t="n">
         <v>1.34</v>
@@ -10893,7 +10893,7 @@
         <v>1.87</v>
       </c>
       <c r="V54" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W54" t="n">
         <v>2.44</v>
@@ -10956,40 +10956,40 @@
         <v>2.46</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AR54" t="n">
         <v>2.46</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AT54" t="n">
         <v>2</v>
       </c>
       <c r="AU54" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.3</v>
+        <v>16</v>
       </c>
       <c r="AW54" t="n">
         <v>2.46</v>
       </c>
       <c r="AX54" t="n">
-        <v>6.8</v>
+        <v>2.08</v>
       </c>
       <c r="AY54" t="n">
         <v>2.08</v>
       </c>
       <c r="AZ54" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BA54" t="n">
         <v>2.46</v>
       </c>
       <c r="BB54" t="n">
-        <v>11</v>
+        <v>2.22</v>
       </c>
       <c r="BC54" t="n">
         <v>2.24</v>
@@ -10998,7 +10998,7 @@
         <v>2.36</v>
       </c>
       <c r="BE54" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BF54" t="n">
         <v>6.8</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -11275,10 +11275,10 @@
         <v>2.66</v>
       </c>
       <c r="T56" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U56" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V56" t="n">
         <v>1.09</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -11448,25 +11448,25 @@
         <v>1.01</v>
       </c>
       <c r="M57" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N57" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="O57" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P57" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q57" t="n">
         <v>1.92</v>
       </c>
       <c r="R57" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S57" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="T57" t="n">
         <v>1.72</v>
@@ -11538,7 +11538,7 @@
         <v>3.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AR57" t="n">
         <v>8</v>
@@ -11562,7 +11562,7 @@
         <v>4</v>
       </c>
       <c r="AY57" t="n">
-        <v>15</v>
+        <v>3.7</v>
       </c>
       <c r="AZ57" t="n">
         <v>3.7</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -11621,16 +11621,16 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G58" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H58" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I58" t="n">
         <v>2.2</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.22</v>
       </c>
       <c r="J58" t="n">
         <v>3.9</v>
@@ -11669,7 +11669,7 @@
         <v>2.76</v>
       </c>
       <c r="V58" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W58" t="n">
         <v>1.41</v>
@@ -11696,7 +11696,7 @@
         <v>10.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF58" t="n">
         <v>27</v>
@@ -11717,13 +11717,13 @@
         <v>32</v>
       </c>
       <c r="AL58" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM58" t="n">
         <v>55</v>
       </c>
       <c r="AN58" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO58" t="n">
         <v>11</v>
@@ -11732,7 +11732,7 @@
         <v>22</v>
       </c>
       <c r="AQ58" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR58" t="n">
         <v>15.5</v>
@@ -11741,7 +11741,7 @@
         <v>27</v>
       </c>
       <c r="AT58" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU58" t="n">
         <v>8.800000000000001</v>
@@ -11750,10 +11750,10 @@
         <v>10</v>
       </c>
       <c r="AW58" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY58" t="n">
         <v>13</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -12012,16 +12012,16 @@
         <v>1.53</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H60" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="I60" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J60" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K60" t="n">
         <v>4.5</v>
@@ -12033,16 +12033,16 @@
         <v>1.06</v>
       </c>
       <c r="N60" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="O60" t="n">
         <v>1.33</v>
       </c>
       <c r="P60" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R60" t="n">
         <v>1.21</v>
@@ -12060,7 +12060,7 @@
         <v>1.11</v>
       </c>
       <c r="W60" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12239,7 @@
         <v>1.83</v>
       </c>
       <c r="R61" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S61" t="n">
         <v>3.1</v>
@@ -12278,7 +12278,7 @@
         <v>16.5</v>
       </c>
       <c r="AE61" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF61" t="n">
         <v>13.5</v>
@@ -12320,7 +12320,7 @@
         <v>26</v>
       </c>
       <c r="AS61" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AT61" t="n">
         <v>9.6</v>
@@ -12356,7 +12356,7 @@
         <v>27</v>
       </c>
       <c r="BE61" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BF61" t="n">
         <v>11</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G62" t="n">
         <v>2.74</v>
@@ -12436,7 +12436,7 @@
         <v>1.24</v>
       </c>
       <c r="S62" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T62" t="n">
         <v>1.93</v>
@@ -12451,13 +12451,13 @@
         <v>1.57</v>
       </c>
       <c r="X62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y62" t="n">
         <v>11</v>
       </c>
       <c r="Z62" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA62" t="n">
         <v>70</v>
@@ -12469,10 +12469,10 @@
         <v>8.4</v>
       </c>
       <c r="AD62" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE62" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF62" t="n">
         <v>19</v>
@@ -12514,10 +12514,10 @@
         <v>18</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AT62" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU62" t="n">
         <v>6.4</v>
@@ -12526,7 +12526,7 @@
         <v>12.5</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX62" t="n">
         <v>14</v>
@@ -12538,29 +12538,29 @@
         <v>17</v>
       </c>
       <c r="BA62" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BB62" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE62" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC62" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD62" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE62" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF62" t="n">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="BG62" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -12979,43 +12979,43 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G65" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="H65" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J65" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="K65" t="n">
         <v>3.6</v>
       </c>
       <c r="L65" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M65" t="n">
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O65" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P65" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q65" t="n">
         <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
@@ -13027,10 +13027,10 @@
         <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W65" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -13087,52 +13087,52 @@
         <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF65" t="n">
         <v>1.01</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
         <v>4.1</v>
@@ -787,13 +787,13 @@
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
         <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
         <v>2.24</v>
@@ -805,10 +805,10 @@
         <v>2.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X2" t="n">
         <v>28</v>
@@ -823,7 +823,7 @@
         <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
         <v>11</v>
@@ -859,10 +859,10 @@
         <v>55</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP2" t="n">
         <v>24</v>
@@ -871,10 +871,10 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
         <v>14</v>
@@ -883,7 +883,7 @@
         <v>9.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW2" t="n">
         <v>32</v>
@@ -898,7 +898,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -910,17 +910,17 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>36</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
         <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,31 +975,31 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.59</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
         <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
         <v>2.76</v>
@@ -1160,7 +1160,7 @@
         <v>2.06</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1172,7 +1172,7 @@
         <v>1.48</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
         <v>1.48</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
         <v>1.98</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J5" t="n">
         <v>4.2</v>
@@ -1357,7 +1357,7 @@
         <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1369,13 +1369,13 @@
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
         <v>2.16</v>
@@ -1387,10 +1387,10 @@
         <v>2.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1399,7 +1399,7 @@
         <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
         <v>26</v>
@@ -1411,7 +1411,7 @@
         <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1423,7 +1423,7 @@
         <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
@@ -1435,7 +1435,7 @@
         <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
         <v>55</v>
@@ -1444,7 +1444,7 @@
         <v>21</v>
       </c>
       <c r="AO5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1456,7 +1456,7 @@
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
         <v>19</v>
@@ -1471,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY5" t="n">
         <v>13.5</v>
@@ -1483,16 +1483,16 @@
         <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>17.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1533,94 +1533,94 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>990</v>
+        <v>11.5</v>
       </c>
       <c r="H6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L6" t="n">
         <v>1.37</v>
       </c>
-      <c r="I6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.27</v>
-      </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
         <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V6" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
@@ -1638,65 +1638,65 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1733,16 @@
         <v>4.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I7" t="n">
         <v>1.98</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.3</v>
@@ -1757,7 +1757,7 @@
         <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
         <v>1.65</v>
@@ -1766,7 +1766,7 @@
         <v>1.59</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
         <v>1.59</v>
@@ -1787,10 +1787,10 @@
         <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB7" t="n">
         <v>30</v>
@@ -1847,16 +1847,16 @@
         <v>19.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1868,7 +1868,7 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
         <v>36</v>
@@ -1883,14 +1883,14 @@
         <v>29</v>
       </c>
       <c r="BF7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BG7" t="n">
         <v>8.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1924,34 +1924,34 @@
         <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
         <v>2.06</v>
@@ -1972,7 +1972,7 @@
         <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2312,85 +2312,85 @@
         <v>2.74</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
         <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L10" t="n">
         <v>1.57</v>
       </c>
       <c r="M10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
         <v>6.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
         <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="n">
         <v>9.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2423,10 +2423,10 @@
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2435,44 +2435,44 @@
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
-        <v>140</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>1.58</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2724,31 +2724,31 @@
         <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
         <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
         <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
         <v>2.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X12" t="n">
         <v>17.5</v>
@@ -2802,7 +2802,7 @@
         <v>26</v>
       </c>
       <c r="AO12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
         <v>13</v>
@@ -2811,10 +2811,10 @@
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>38</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
         <v>15.5</v>
@@ -2841,10 +2841,10 @@
         <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD12" t="n">
         <v>4.2</v>
@@ -2853,14 +2853,14 @@
         <v>4.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="I13" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.42</v>
@@ -2915,16 +2915,16 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O13" t="n">
         <v>1.02</v>
       </c>
       <c r="P13" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
         <v>1.08</v>
@@ -2933,16 +2933,16 @@
         <v>2.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W13" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3091,16 +3091,16 @@
         <v>6.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.26</v>
@@ -3112,37 +3112,37 @@
         <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
         <v>2.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
         <v>2.46</v>
       </c>
       <c r="T14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3196,7 +3196,7 @@
         <v>4.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
         <v>3.7</v>
@@ -3205,16 +3205,16 @@
         <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>4.6</v>
@@ -3223,32 +3223,32 @@
         <v>4.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC14" t="n">
         <v>4.7</v>
       </c>
       <c r="BD14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE14" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H15" t="n">
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>500</v>
+        <v>870</v>
       </c>
       <c r="J15" t="n">
         <v>1.03</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="G16" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H16" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="I16" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
         <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3629,14 +3629,14 @@
         <v>4.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG16" t="n">
         <v>4.3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3670,40 +3670,40 @@
         <v>2.28</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H17" t="n">
         <v>3.25</v>
       </c>
       <c r="I17" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.78</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
         <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
         <v>3.75</v>
@@ -3712,7 +3712,7 @@
         <v>1.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>1.35</v>
@@ -3790,7 +3790,7 @@
         <v>3.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.8</v>
+        <v>2.96</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
@@ -3808,7 +3808,7 @@
         <v>3.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
         <v>3.9</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3876,16 +3876,16 @@
         <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
@@ -3897,7 +3897,7 @@
         <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
         <v>2.84</v>
@@ -3915,7 +3915,7 @@
         <v>2.66</v>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
         <v>26</v>
@@ -3924,31 +3924,31 @@
         <v>65</v>
       </c>
       <c r="AA18" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE18" t="n">
         <v>120</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
         <v>15</v>
@@ -3963,7 +3963,7 @@
         <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO18" t="n">
         <v>140</v>
@@ -3975,10 +3975,10 @@
         <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,7 +3990,7 @@
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AX18" t="n">
         <v>8.199999999999999</v>
@@ -4002,7 +4002,7 @@
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -4011,20 +4011,20 @@
         <v>13.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G19" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="H19" t="n">
-        <v>38</v>
+        <v>19.5</v>
       </c>
       <c r="I19" t="n">
         <v>55</v>
       </c>
       <c r="J19" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="K19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
@@ -4088,25 +4088,25 @@
         <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R19" t="n">
         <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="X19" t="n">
         <v>26</v>
@@ -4121,10 +4121,10 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AD19" t="n">
         <v>200</v>
@@ -4133,10 +4133,10 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH19" t="n">
         <v>110</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU19" t="n">
         <v>20</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AV19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW19" t="n">
         <v>8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
         <v>4.7</v>
       </c>
       <c r="AY19" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
         <v>1.03</v>
       </c>
       <c r="K20" t="n">
-        <v>980</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,13 +4273,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.26</v>
@@ -4291,10 +4291,10 @@
         <v>1.26</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4443,58 +4443,58 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="G21" t="n">
         <v>3.6</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I21" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="J21" t="n">
         <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T21" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
         <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -4551,62 +4551,62 @@
         <v>26</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU21" t="n">
         <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.79</v>
+        <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.94</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.31</v>
+        <v>30</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.31</v>
+        <v>5.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G22" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
         <v>6.4</v>
       </c>
       <c r="J22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K22" t="n">
         <v>4.9</v>
@@ -4670,16 +4670,16 @@
         <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="T22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U22" t="n">
         <v>2.18</v>
@@ -4688,7 +4688,7 @@
         <v>1.18</v>
       </c>
       <c r="W22" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X22" t="n">
         <v>24</v>
@@ -4709,7 +4709,7 @@
         <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
         <v>75</v>
@@ -4739,7 +4739,7 @@
         <v>90</v>
       </c>
       <c r="AN22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO22" t="n">
         <v>75</v>
@@ -4751,10 +4751,10 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
         <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>9.800000000000001</v>
@@ -4778,7 +4778,7 @@
         <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB22" t="n">
         <v>13</v>
@@ -4790,7 +4790,7 @@
         <v>24</v>
       </c>
       <c r="BE22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF22" t="n">
         <v>5.8</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="H23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I23" t="n">
         <v>3.6</v>
@@ -4846,7 +4846,7 @@
         <v>3.85</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.3</v>
@@ -4855,7 +4855,7 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
         <v>1.21</v>
@@ -4876,7 +4876,7 @@
         <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V23" t="n">
         <v>1.38</v>
@@ -4897,7 +4897,7 @@
         <v>65</v>
       </c>
       <c r="AB23" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC23" t="n">
         <v>10.5</v>
@@ -4948,7 +4948,7 @@
         <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
@@ -4960,7 +4960,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX23" t="n">
         <v>13</v>
@@ -4972,7 +4972,7 @@
         <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4984,17 +4984,17 @@
         <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG23" t="n">
         <v>19</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>6.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I24" t="n">
         <v>1.68</v>
@@ -5112,7 +5112,7 @@
         <v>30</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
         <v>260</v>
@@ -5121,7 +5121,7 @@
         <v>140</v>
       </c>
       <c r="AL24" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>240</v>
@@ -5145,7 +5145,7 @@
         <v>14.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU24" t="n">
         <v>8.199999999999999</v>
@@ -5154,7 +5154,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX24" t="n">
         <v>46</v>
@@ -5166,7 +5166,7 @@
         <v>27</v>
       </c>
       <c r="BA24" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BB24" t="n">
         <v>48</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5228,13 +5228,13 @@
         <v>2.34</v>
       </c>
       <c r="I25" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J25" t="n">
         <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5252,7 +5252,7 @@
         <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R25" t="n">
         <v>1.42</v>
@@ -5261,13 +5261,13 @@
         <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U25" t="n">
         <v>2.28</v>
       </c>
       <c r="V25" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W25" t="n">
         <v>1.44</v>
@@ -5276,13 +5276,13 @@
         <v>20</v>
       </c>
       <c r="Y25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
         <v>17</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB25" t="n">
         <v>14</v>
@@ -5306,10 +5306,10 @@
         <v>16.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK25" t="n">
         <v>34</v>
@@ -5336,7 +5336,7 @@
         <v>14.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AT25" t="n">
         <v>12</v>
@@ -5351,7 +5351,7 @@
         <v>21</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY25" t="n">
         <v>11.5</v>
@@ -5363,16 +5363,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD25" t="n">
         <v>8</v>
       </c>
-      <c r="BC25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE25" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF25" t="n">
         <v>20</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>2.32</v>
       </c>
       <c r="G26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I26" t="n">
         <v>3.85</v>
@@ -5428,7 +5428,7 @@
         <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,22 +5437,22 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1.42</v>
       </c>
       <c r="P26" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q26" t="n">
         <v>2.26</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
         <v>1.9</v>
@@ -5464,7 +5464,7 @@
         <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X26" t="n">
         <v>13</v>
@@ -5473,28 +5473,28 @@
         <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26" t="n">
         <v>7.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
@@ -5506,16 +5506,16 @@
         <v>38</v>
       </c>
       <c r="AK26" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -5530,7 +5530,7 @@
         <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT26" t="n">
         <v>6.4</v>
@@ -5542,7 +5542,7 @@
         <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5554,29 +5554,29 @@
         <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
         <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BF26" t="n">
         <v>20</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H27" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I27" t="n">
         <v>2.34</v>
@@ -5622,7 +5622,7 @@
         <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
         <v>1.33</v>
@@ -5655,7 +5655,7 @@
         <v>2.38</v>
       </c>
       <c r="V27" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W27" t="n">
         <v>1.4</v>
@@ -5697,10 +5697,10 @@
         <v>32</v>
       </c>
       <c r="AJ27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL27" t="n">
         <v>40</v>
@@ -5709,13 +5709,13 @@
         <v>70</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO27" t="n">
         <v>970</v>
       </c>
       <c r="AP27" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
         <v>9.6</v>
@@ -5724,19 +5724,19 @@
         <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX27" t="n">
         <v>19</v>
@@ -5748,19 +5748,19 @@
         <v>12</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="BB27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD27" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF27" t="n">
         <v>19.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G28" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5998,19 +5998,19 @@
         <v>3.2</v>
       </c>
       <c r="G29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J29" t="n">
         <v>3.55</v>
       </c>
-      <c r="H29" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6040,13 +6040,13 @@
         <v>1.64</v>
       </c>
       <c r="U29" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V29" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W29" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
         <v>22</v>
@@ -6058,7 +6058,7 @@
         <v>970</v>
       </c>
       <c r="AA29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB29" t="n">
         <v>970</v>
@@ -6073,7 +6073,7 @@
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG29" t="n">
         <v>14.5</v>
@@ -6085,10 +6085,10 @@
         <v>34</v>
       </c>
       <c r="AJ29" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL29" t="n">
         <v>42</v>
@@ -6097,13 +6097,13 @@
         <v>70</v>
       </c>
       <c r="AN29" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO29" t="n">
         <v>970</v>
       </c>
       <c r="AP29" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ29" t="n">
         <v>9.4</v>
@@ -6112,7 +6112,7 @@
         <v>12.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT29" t="n">
         <v>11.5</v>
@@ -6136,19 +6136,19 @@
         <v>12</v>
       </c>
       <c r="BA29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF29" t="n">
         <v>20</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H30" t="n">
         <v>2.14</v>
@@ -6207,19 +6207,19 @@
         <v>3.65</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M30" t="n">
         <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
         <v>1.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
         <v>2.18</v>
@@ -6228,13 +6228,13 @@
         <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T30" t="n">
         <v>1.89</v>
       </c>
       <c r="U30" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
@@ -6249,7 +6249,7 @@
         <v>9.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
         <v>36</v>
@@ -6267,7 +6267,7 @@
         <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG30" t="n">
         <v>18.5</v>
@@ -6300,37 +6300,37 @@
         <v>8.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS30" t="n">
         <v>5.1</v>
       </c>
       <c r="AT30" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU30" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AW30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX30" t="n">
         <v>21</v>
       </c>
-      <c r="AX30" t="n">
-        <v>20</v>
-      </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -6348,11 +6348,11 @@
         <v>4.9</v>
       </c>
       <c r="BG30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6383,170 +6383,170 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="G31" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H31" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="I31" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV31" t="n">
         <v>8</v>
       </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G32" t="n">
         <v>4.3</v>
@@ -6592,37 +6592,37 @@
         <v>3.35</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>1.38</v>
       </c>
       <c r="P32" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
         <v>2.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
         <v>3.9</v>
       </c>
       <c r="T32" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U32" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
         <v>1.87</v>
@@ -6664,7 +6664,7 @@
         <v>19.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ32" t="n">
         <v>110</v>
@@ -6676,7 +6676,7 @@
         <v>65</v>
       </c>
       <c r="AM32" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN32" t="n">
         <v>65</v>
@@ -6718,7 +6718,7 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB32" t="n">
         <v>10</v>
@@ -6727,20 +6727,20 @@
         <v>9.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE32" t="n">
         <v>10</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG32" t="n">
         <v>14.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H33" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I33" t="n">
         <v>2.56</v>
@@ -6792,34 +6792,34 @@
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
         <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
         <v>1.46</v>
       </c>
       <c r="R33" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S33" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="T33" t="n">
         <v>1.45</v>
       </c>
       <c r="U33" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V33" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W33" t="n">
         <v>1.45</v>
@@ -6849,7 +6849,7 @@
         <v>25</v>
       </c>
       <c r="AF33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG33" t="n">
         <v>970</v>
@@ -6879,62 +6879,62 @@
         <v>12</v>
       </c>
       <c r="AP33" t="n">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="AQ33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR33" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR33" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AS33" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.6</v>
+        <v>3.95</v>
       </c>
       <c r="AW33" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY33" t="n">
         <v>4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE33" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC33" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="G34" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I34" t="n">
         <v>3.35</v>
@@ -6980,7 +6980,7 @@
         <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6989,7 +6989,7 @@
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>1.86</v>
+        <v>2.84</v>
       </c>
       <c r="O34" t="n">
         <v>1.28</v>
@@ -6998,25 +6998,25 @@
         <v>1.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
         <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G35" t="n">
         <v>3.15</v>
       </c>
       <c r="H35" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I35" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J35" t="n">
         <v>3.1</v>
@@ -7180,7 +7180,7 @@
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N35" t="n">
         <v>3.05</v>
@@ -7207,7 +7207,7 @@
         <v>1.84</v>
       </c>
       <c r="V35" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W35" t="n">
         <v>1.48</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G36" t="n">
         <v>2.56</v>
       </c>
       <c r="H36" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I36" t="n">
         <v>3.75</v>
@@ -7371,13 +7371,13 @@
         <v>3.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
         <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O36" t="n">
         <v>1.42</v>
@@ -7413,13 +7413,13 @@
         <v>13</v>
       </c>
       <c r="Z36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA36" t="n">
         <v>80</v>
       </c>
       <c r="AB36" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC36" t="n">
         <v>7.6</v>
@@ -7431,25 +7431,25 @@
         <v>50</v>
       </c>
       <c r="AF36" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI36" t="n">
         <v>75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK36" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL36" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM36" t="n">
         <v>150</v>
@@ -7458,7 +7458,7 @@
         <v>30</v>
       </c>
       <c r="AO36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP36" t="n">
         <v>9.199999999999999</v>
@@ -7470,7 +7470,7 @@
         <v>20</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT36" t="n">
         <v>7.4</v>
@@ -7482,7 +7482,7 @@
         <v>12.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX36" t="n">
         <v>12.5</v>
@@ -7494,29 +7494,29 @@
         <v>17</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF36" t="n">
         <v>22</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
         <v>2.76</v>
       </c>
       <c r="H37" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I37" t="n">
         <v>3.1</v>
@@ -7562,58 +7562,58 @@
         <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>3.2</v>
       </c>
       <c r="O37" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P37" t="n">
         <v>1.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="T37" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="U37" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>1.48</v>
       </c>
       <c r="W37" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y37" t="n">
         <v>11.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA37" t="n">
         <v>55</v>
       </c>
       <c r="AB37" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC37" t="n">
         <v>8</v>
@@ -7625,19 +7625,19 @@
         <v>38</v>
       </c>
       <c r="AF37" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG37" t="n">
         <v>12.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI37" t="n">
         <v>55</v>
       </c>
       <c r="AJ37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK37" t="n">
         <v>34</v>
@@ -7655,62 +7655,62 @@
         <v>38</v>
       </c>
       <c r="AP37" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AQ37" t="n">
         <v>9.6</v>
       </c>
       <c r="AR37" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AT37" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV37" t="n">
         <v>11.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AX37" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="AY37" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="BA37" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BB37" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="BD37" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="BF37" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BG37" t="n">
         <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G38" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="H38" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J38" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K38" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L38" t="n">
         <v>1.48</v>
@@ -7765,7 +7765,7 @@
         <v>1.12</v>
       </c>
       <c r="N38" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O38" t="n">
         <v>1.49</v>
@@ -7789,25 +7789,25 @@
         <v>1.81</v>
       </c>
       <c r="V38" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W38" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="X38" t="n">
         <v>10.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z38" t="n">
         <v>28</v>
       </c>
       <c r="AA38" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC38" t="n">
         <v>8</v>
@@ -7816,10 +7816,10 @@
         <v>18.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF38" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG38" t="n">
         <v>13.5</v>
@@ -7828,7 +7828,7 @@
         <v>23</v>
       </c>
       <c r="AI38" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ38" t="n">
         <v>40</v>
@@ -7837,28 +7837,28 @@
         <v>36</v>
       </c>
       <c r="AL38" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM38" t="n">
         <v>190</v>
       </c>
       <c r="AN38" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO38" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP38" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ38" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT38" t="n">
         <v>6.8</v>
@@ -7870,7 +7870,7 @@
         <v>13.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX38" t="n">
         <v>12.5</v>
@@ -7885,26 +7885,26 @@
         <v>55</v>
       </c>
       <c r="BB38" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BD38" t="n">
         <v>44</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BF38" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H39" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I39" t="n">
         <v>3.05</v>
@@ -7950,7 +7950,7 @@
         <v>3.45</v>
       </c>
       <c r="K39" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L39" t="n">
         <v>1.33</v>
@@ -7962,31 +7962,31 @@
         <v>4.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P39" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="R39" t="n">
         <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="T39" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U39" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V39" t="n">
         <v>1.49</v>
       </c>
       <c r="W39" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X39" t="n">
         <v>22</v>
@@ -8001,10 +8001,10 @@
         <v>44</v>
       </c>
       <c r="AB39" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD39" t="n">
         <v>13.5</v>
@@ -8013,7 +8013,7 @@
         <v>29</v>
       </c>
       <c r="AF39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AG39" t="n">
         <v>13</v>
@@ -8031,10 +8031,10 @@
         <v>27</v>
       </c>
       <c r="AL39" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM39" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN39" t="n">
         <v>18</v>
@@ -8049,22 +8049,22 @@
         <v>13</v>
       </c>
       <c r="AR39" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AS39" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="AT39" t="n">
         <v>12</v>
       </c>
       <c r="AU39" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV39" t="n">
         <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX39" t="n">
         <v>17</v>
@@ -8076,19 +8076,19 @@
         <v>12.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC39" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BD39" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF39" t="n">
         <v>13</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G40" t="n">
         <v>3.2</v>
@@ -8144,7 +8144,7 @@
         <v>3.8</v>
       </c>
       <c r="K40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L40" t="n">
         <v>1.26</v>
@@ -8177,7 +8177,7 @@
         <v>2.48</v>
       </c>
       <c r="V40" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W40" t="n">
         <v>1.45</v>
@@ -8186,7 +8186,7 @@
         <v>27</v>
       </c>
       <c r="Y40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z40" t="n">
         <v>22</v>
@@ -8195,13 +8195,13 @@
         <v>38</v>
       </c>
       <c r="AB40" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD40" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE40" t="n">
         <v>27</v>
@@ -8210,19 +8210,19 @@
         <v>29</v>
       </c>
       <c r="AG40" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH40" t="n">
         <v>18.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AJ40" t="n">
         <v>60</v>
       </c>
       <c r="AK40" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL40" t="n">
         <v>42</v>
@@ -8237,7 +8237,7 @@
         <v>16</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AQ40" t="n">
         <v>10.5</v>
@@ -8246,7 +8246,7 @@
         <v>15.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AT40" t="n">
         <v>12</v>
@@ -8258,7 +8258,7 @@
         <v>10</v>
       </c>
       <c r="AW40" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AX40" t="n">
         <v>20</v>
@@ -8273,16 +8273,16 @@
         <v>21</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC40" t="n">
         <v>21</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.2</v>
+        <v>42</v>
       </c>
       <c r="BF40" t="n">
         <v>14.5</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G41" t="n">
         <v>1.67</v>
@@ -8359,16 +8359,16 @@
         <v>1.37</v>
       </c>
       <c r="R41" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S41" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="T41" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U41" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V41" t="n">
         <v>1.19</v>
@@ -8389,7 +8389,7 @@
         <v>140</v>
       </c>
       <c r="AB41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC41" t="n">
         <v>16.5</v>
@@ -8404,7 +8404,7 @@
         <v>18</v>
       </c>
       <c r="AG41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH41" t="n">
         <v>21</v>
@@ -8431,16 +8431,16 @@
         <v>42</v>
       </c>
       <c r="AP41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ41" t="n">
         <v>4</v>
       </c>
-      <c r="AQ41" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AR41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT41" t="n">
         <v>14</v>
@@ -8452,7 +8452,7 @@
         <v>19</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX41" t="n">
         <v>10.5</v>
@@ -8464,7 +8464,7 @@
         <v>12.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB41" t="n">
         <v>14.5</v>
@@ -8476,17 +8476,17 @@
         <v>16.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF41" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG41" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G42" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H42" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J42" t="n">
         <v>4.5</v>
       </c>
       <c r="K42" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L42" t="n">
         <v>1.17</v>
@@ -8565,10 +8565,10 @@
         <v>2.98</v>
       </c>
       <c r="V42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W42" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
         <v>55</v>
@@ -8580,7 +8580,7 @@
         <v>22</v>
       </c>
       <c r="AA42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB42" t="n">
         <v>38</v>
@@ -8607,7 +8607,7 @@
         <v>27</v>
       </c>
       <c r="AJ42" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK42" t="n">
         <v>46</v>
@@ -8619,22 +8619,22 @@
         <v>55</v>
       </c>
       <c r="AN42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AQ42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS42" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AT42" t="n">
         <v>22</v>
@@ -8643,13 +8643,13 @@
         <v>9.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW42" t="n">
         <v>12</v>
       </c>
       <c r="AX42" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="AY42" t="n">
         <v>13.5</v>
@@ -8661,26 +8661,26 @@
         <v>15.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>50</v>
+        <v>3.8</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BF42" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG42" t="n">
         <v>4.4</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G43" t="n">
         <v>1.91</v>
@@ -8720,46 +8720,46 @@
         <v>4.7</v>
       </c>
       <c r="I43" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J43" t="n">
         <v>3.75</v>
       </c>
       <c r="K43" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N43" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O43" t="n">
         <v>1.16</v>
       </c>
       <c r="P43" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q43" t="n">
         <v>1.46</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S43" t="n">
         <v>2.28</v>
       </c>
       <c r="T43" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U43" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V43" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W43" t="n">
         <v>2.08</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8905,16 +8905,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G44" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="H44" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I44" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>4</v>
@@ -8923,16 +8923,16 @@
         <v>4.6</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M44" t="n">
         <v>1.02</v>
       </c>
       <c r="N44" t="n">
-        <v>2.76</v>
+        <v>6</v>
       </c>
       <c r="O44" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="P44" t="n">
         <v>2.76</v>
@@ -8941,134 +8941,134 @@
         <v>1.47</v>
       </c>
       <c r="R44" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="S44" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="V44" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W44" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y44" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC44" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI44" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G45" t="n">
         <v>2.16</v>
@@ -9114,28 +9114,28 @@
         <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L45" t="n">
         <v>1.23</v>
       </c>
       <c r="M45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N45" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P45" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q45" t="n">
         <v>1.47</v>
       </c>
       <c r="R45" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S45" t="n">
         <v>2.16</v>
@@ -9144,7 +9144,7 @@
         <v>1.48</v>
       </c>
       <c r="U45" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V45" t="n">
         <v>1.35</v>
@@ -9168,7 +9168,7 @@
         <v>18.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD45" t="n">
         <v>18.5</v>
@@ -9204,16 +9204,16 @@
         <v>9.6</v>
       </c>
       <c r="AO45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="AQ45" t="n">
         <v>17</v>
       </c>
       <c r="AR45" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS45" t="n">
         <v>4.7</v>
@@ -9222,7 +9222,7 @@
         <v>12</v>
       </c>
       <c r="AU45" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV45" t="n">
         <v>12</v>
@@ -9249,20 +9249,20 @@
         <v>14</v>
       </c>
       <c r="BD45" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF45" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9296,19 +9296,19 @@
         <v>2.48</v>
       </c>
       <c r="G46" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I46" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="K46" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9323,13 +9323,13 @@
         <v>1.15</v>
       </c>
       <c r="P46" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q46" t="n">
         <v>1.54</v>
       </c>
       <c r="R46" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S46" t="n">
         <v>2.34</v>
@@ -9338,13 +9338,13 @@
         <v>1.51</v>
       </c>
       <c r="U46" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V46" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X46" t="n">
         <v>34</v>
@@ -9380,7 +9380,7 @@
         <v>1000</v>
       </c>
       <c r="AI46" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ46" t="n">
         <v>50</v>
@@ -9419,7 +9419,7 @@
         <v>1.84</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AW46" t="n">
         <v>2</v>
@@ -9434,7 +9434,7 @@
         <v>2.12</v>
       </c>
       <c r="BA46" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB46" t="n">
         <v>2.04</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         <v>2.08</v>
       </c>
       <c r="H47" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I47" t="n">
         <v>4.6</v>
@@ -9502,7 +9502,7 @@
         <v>3.7</v>
       </c>
       <c r="K47" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.3</v>
@@ -9511,28 +9511,28 @@
         <v>1.05</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P47" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R47" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U47" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V47" t="n">
         <v>1.28</v>
@@ -9544,19 +9544,19 @@
         <v>21</v>
       </c>
       <c r="Y47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z47" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA47" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB47" t="n">
         <v>12.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD47" t="n">
         <v>21</v>
@@ -9571,7 +9571,7 @@
         <v>13</v>
       </c>
       <c r="AH47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI47" t="n">
         <v>65</v>
@@ -9583,19 +9583,19 @@
         <v>25</v>
       </c>
       <c r="AL47" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
       </c>
       <c r="AN47" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO47" t="n">
         <v>60</v>
       </c>
       <c r="AP47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ47" t="n">
         <v>12</v>
@@ -9616,7 +9616,7 @@
         <v>12</v>
       </c>
       <c r="AW47" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX47" t="n">
         <v>9.6</v>
@@ -9628,7 +9628,7 @@
         <v>12.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB47" t="n">
         <v>16.5</v>
@@ -9643,14 +9643,14 @@
         <v>4</v>
       </c>
       <c r="BF47" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG47" t="n">
-        <v>3.9</v>
+        <v>34</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
         <v>3.35</v>
       </c>
       <c r="H48" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I48" t="n">
         <v>2.66</v>
@@ -9696,7 +9696,7 @@
         <v>3.2</v>
       </c>
       <c r="K48" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L48" t="n">
         <v>1.44</v>
@@ -9711,7 +9711,7 @@
         <v>1.36</v>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q48" t="n">
         <v>2.08</v>
@@ -9810,7 +9810,7 @@
         <v>10.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX48" t="n">
         <v>18.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G49" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H49" t="n">
         <v>3.5</v>
@@ -9887,10 +9887,10 @@
         <v>4.1</v>
       </c>
       <c r="J49" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K49" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9899,16 +9899,16 @@
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>1.28</v>
       </c>
       <c r="P49" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R49" t="n">
         <v>1.37</v>
@@ -9923,10 +9923,10 @@
         <v>1.11</v>
       </c>
       <c r="V49" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W49" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X49" t="n">
         <v>1000</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10072,13 +10072,13 @@
         <v>1.99</v>
       </c>
       <c r="G50" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I50" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>4.3</v>
@@ -10114,19 +10114,19 @@
         <v>1.44</v>
       </c>
       <c r="U50" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V50" t="n">
         <v>1.36</v>
       </c>
       <c r="W50" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X50" t="n">
         <v>34</v>
       </c>
       <c r="Y50" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Z50" t="n">
         <v>36</v>
@@ -10138,7 +10138,7 @@
         <v>19</v>
       </c>
       <c r="AC50" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD50" t="n">
         <v>16</v>
@@ -10150,7 +10150,7 @@
         <v>18</v>
       </c>
       <c r="AG50" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH50" t="n">
         <v>14</v>
@@ -10174,7 +10174,7 @@
         <v>7</v>
       </c>
       <c r="AO50" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP50" t="n">
         <v>28</v>
@@ -10225,14 +10225,14 @@
         <v>36</v>
       </c>
       <c r="BF50" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG50" t="n">
         <v>16.5</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.6</v>
       </c>
       <c r="G51" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="H51" t="n">
         <v>4.7</v>
@@ -10275,7 +10275,7 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K51" t="n">
         <v>6.2</v>
@@ -10287,13 +10287,13 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="O51" t="n">
         <v>1.02</v>
       </c>
       <c r="P51" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Q51" t="n">
         <v>2.1</v>
@@ -10314,7 +10314,7 @@
         <v>1.06</v>
       </c>
       <c r="W51" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10481,10 +10481,10 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="O52" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="P52" t="n">
         <v>1.43</v>
@@ -10496,13 +10496,13 @@
         <v>1.18</v>
       </c>
       <c r="S52" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V52" t="n">
         <v>1.27</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G53" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="H53" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I53" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J53" t="n">
         <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -10696,13 +10696,13 @@
         <v>1.84</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V53" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W53" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="X53" t="n">
         <v>14</v>
@@ -10750,7 +10750,7 @@
         <v>48</v>
       </c>
       <c r="AM53" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN53" t="n">
         <v>36</v>
@@ -10765,7 +10765,7 @@
         <v>9.6</v>
       </c>
       <c r="AR53" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS53" t="n">
         <v>5.1</v>
@@ -10774,7 +10774,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU53" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV53" t="n">
         <v>12</v>
@@ -10789,16 +10789,16 @@
         <v>10.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB53" t="n">
         <v>32</v>
       </c>
       <c r="BC53" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD53" t="n">
         <v>4.8</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="G54" t="n">
         <v>1.42</v>
@@ -10860,7 +10860,7 @@
         <v>5.5</v>
       </c>
       <c r="K54" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -10869,22 +10869,22 @@
         <v>1.02</v>
       </c>
       <c r="N54" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O54" t="n">
         <v>1.13</v>
       </c>
       <c r="P54" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R54" t="n">
         <v>1.6</v>
       </c>
       <c r="S54" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="T54" t="n">
         <v>1.01</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11051,13 +11051,13 @@
         <v>2.46</v>
       </c>
       <c r="J55" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K55" t="n">
         <v>3.85</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M55" t="n">
         <v>1.06</v>
@@ -11072,13 +11072,13 @@
         <v>1.89</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R55" t="n">
         <v>1.34</v>
       </c>
       <c r="S55" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T55" t="n">
         <v>1.66</v>
@@ -11126,13 +11126,13 @@
         <v>970</v>
       </c>
       <c r="AI55" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ55" t="n">
         <v>70</v>
       </c>
       <c r="AK55" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL55" t="n">
         <v>55</v>
@@ -11141,7 +11141,7 @@
         <v>110</v>
       </c>
       <c r="AN55" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO55" t="n">
         <v>21</v>
@@ -11156,7 +11156,7 @@
         <v>12</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT55" t="n">
         <v>10</v>
@@ -11189,7 +11189,7 @@
         <v>5.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE55" t="n">
         <v>6</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11233,46 +11233,46 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="G56" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="I56" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S56" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K56" t="n">
-        <v>950</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S56" t="n">
-        <v>3</v>
       </c>
       <c r="T56" t="n">
         <v>1.72</v>
@@ -11284,7 +11284,7 @@
         <v>2.12</v>
       </c>
       <c r="W56" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X56" t="n">
         <v>17.5</v>
@@ -11296,7 +11296,7 @@
         <v>13</v>
       </c>
       <c r="AA56" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB56" t="n">
         <v>21</v>
@@ -11341,7 +11341,7 @@
         <v>15</v>
       </c>
       <c r="AP56" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ56" t="n">
         <v>7.2</v>
@@ -11359,7 +11359,7 @@
         <v>6.4</v>
       </c>
       <c r="AV56" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AW56" t="n">
         <v>3.75</v>
@@ -11368,16 +11368,16 @@
         <v>4.2</v>
       </c>
       <c r="AY56" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA56" t="n">
         <v>4.2</v>
       </c>
       <c r="BB56" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC56" t="n">
         <v>4.2</v>
@@ -11386,17 +11386,17 @@
         <v>4.2</v>
       </c>
       <c r="BE56" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF56" t="n">
         <v>4.2</v>
       </c>
       <c r="BG56" t="n">
-        <v>3.35</v>
+        <v>9</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11427,16 +11427,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G57" t="n">
         <v>2.32</v>
       </c>
       <c r="H57" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I57" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J57" t="n">
         <v>3.2</v>
@@ -11475,7 +11475,7 @@
         <v>1.8</v>
       </c>
       <c r="V57" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W57" t="n">
         <v>1.75</v>
@@ -11502,7 +11502,7 @@
         <v>17</v>
       </c>
       <c r="AE57" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF57" t="n">
         <v>13</v>
@@ -11517,7 +11517,7 @@
         <v>90</v>
       </c>
       <c r="AJ57" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK57" t="n">
         <v>32</v>
@@ -11541,7 +11541,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS57" t="n">
         <v>36</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11621,94 +11621,94 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="H58" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="I58" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="J58" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K58" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
       </c>
       <c r="M58" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N58" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="O58" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P58" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R58" t="n">
         <v>1.33</v>
       </c>
       <c r="S58" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T58" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U58" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V58" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="W58" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X58" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y58" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z58" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA58" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AB58" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC58" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD58" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF58" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG58" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH58" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI58" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ58" t="n">
         <v>1000</v>
@@ -11717,7 +11717,7 @@
         <v>1000</v>
       </c>
       <c r="AL58" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM58" t="n">
         <v>1000</v>
@@ -11726,65 +11726,65 @@
         <v>1000</v>
       </c>
       <c r="AO58" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11815,61 +11815,61 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="G59" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="J59" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q59" t="n">
         <v>2.42</v>
-      </c>
-      <c r="K59" t="n">
-        <v>950</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N59" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1.56</v>
       </c>
       <c r="R59" t="n">
         <v>1.2</v>
       </c>
       <c r="S59" t="n">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="T59" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V59" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W59" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X59" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y59" t="n">
         <v>1000</v>
@@ -11923,62 +11923,62 @@
         <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.11</v>
+        <v>7</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.11</v>
+        <v>5.7</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.11</v>
+        <v>34</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="AU59" t="n">
-        <v>1.11</v>
+        <v>4</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.11</v>
+        <v>10</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.11</v>
+        <v>7</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.11</v>
+        <v>17</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.11</v>
+        <v>6.8</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.11</v>
+        <v>3.95</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12015,22 +12015,22 @@
         <v>1.38</v>
       </c>
       <c r="H60" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I60" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="J60" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K60" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L60" t="n">
         <v>1.32</v>
       </c>
       <c r="M60" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N60" t="n">
         <v>4.1</v>
@@ -12039,7 +12039,7 @@
         <v>1.24</v>
       </c>
       <c r="P60" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q60" t="n">
         <v>1.65</v>
@@ -12048,10 +12048,10 @@
         <v>1.43</v>
       </c>
       <c r="S60" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T60" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U60" t="n">
         <v>1.68</v>
@@ -12066,7 +12066,7 @@
         <v>21</v>
       </c>
       <c r="Y60" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z60" t="n">
         <v>110</v>
@@ -12099,7 +12099,7 @@
         <v>190</v>
       </c>
       <c r="AJ60" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AK60" t="n">
         <v>15</v>
@@ -12111,46 +12111,46 @@
         <v>210</v>
       </c>
       <c r="AN60" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AO60" t="n">
         <v>270</v>
       </c>
       <c r="AP60" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AQ60" t="n">
         <v>24</v>
       </c>
       <c r="AR60" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AS60" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AT60" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU60" t="n">
         <v>11.5</v>
       </c>
       <c r="AV60" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AW60" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX60" t="n">
         <v>7</v>
       </c>
       <c r="AY60" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ60" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA60" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB60" t="n">
         <v>9.6</v>
@@ -12162,17 +12162,17 @@
         <v>29</v>
       </c>
       <c r="BE60" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF60" t="n">
         <v>5</v>
       </c>
       <c r="BG60" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12203,22 +12203,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="G61" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H61" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I61" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K61" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12227,34 +12227,34 @@
         <v>1.07</v>
       </c>
       <c r="N61" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O61" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P61" t="n">
         <v>1.91</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="R61" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S61" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T61" t="n">
         <v>1.96</v>
       </c>
       <c r="U61" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V61" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W61" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -12269,10 +12269,10 @@
         <v>1000</v>
       </c>
       <c r="AB61" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC61" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD61" t="n">
         <v>1000</v>
@@ -12281,92 +12281,92 @@
         <v>1000</v>
       </c>
       <c r="AF61" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG61" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC61" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BD61" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE61" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="BF61" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG61" t="n">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G62" t="n">
         <v>2.04</v>
@@ -12457,7 +12457,7 @@
         <v>17</v>
       </c>
       <c r="Z62" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA62" t="n">
         <v>85</v>
@@ -12484,7 +12484,7 @@
         <v>17</v>
       </c>
       <c r="AI62" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ62" t="n">
         <v>23</v>
@@ -12544,7 +12544,7 @@
         <v>20</v>
       </c>
       <c r="BC62" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD62" t="n">
         <v>28</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12791,10 +12791,10 @@
         <v>3.45</v>
       </c>
       <c r="H64" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J64" t="n">
         <v>3.9</v>
@@ -12818,7 +12818,7 @@
         <v>2.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R64" t="n">
         <v>1.64</v>
@@ -12830,13 +12830,13 @@
         <v>1.54</v>
       </c>
       <c r="U64" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V64" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W64" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X64" t="n">
         <v>25</v>
@@ -12860,7 +12860,7 @@
         <v>10.5</v>
       </c>
       <c r="AE64" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF64" t="n">
         <v>27</v>
@@ -12926,7 +12926,7 @@
         <v>13.5</v>
       </c>
       <c r="BA64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB64" t="n">
         <v>48</v>
@@ -12944,11 +12944,11 @@
         <v>20</v>
       </c>
       <c r="BG64" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12994,7 @@
         <v>3.7</v>
       </c>
       <c r="K65" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -13003,28 +13003,28 @@
         <v>1.07</v>
       </c>
       <c r="N65" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O65" t="n">
         <v>1.34</v>
       </c>
       <c r="P65" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R65" t="n">
         <v>1.33</v>
       </c>
       <c r="S65" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U65" t="n">
         <v>1.94</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.92</v>
       </c>
       <c r="V65" t="n">
         <v>1.19</v>
@@ -13093,7 +13093,7 @@
         <v>15.5</v>
       </c>
       <c r="AR65" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS65" t="n">
         <v>11</v>
@@ -13117,19 +13117,19 @@
         <v>9</v>
       </c>
       <c r="AZ65" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA65" t="n">
         <v>10.5</v>
       </c>
       <c r="BB65" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC65" t="n">
         <v>7.4</v>
       </c>
       <c r="BD65" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE65" t="n">
         <v>11</v>
@@ -13138,11 +13138,11 @@
         <v>10.5</v>
       </c>
       <c r="BG65" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13173,22 +13173,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G66" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H66" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I66" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J66" t="n">
         <v>3.65</v>
       </c>
       <c r="K66" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
@@ -13197,28 +13197,28 @@
         <v>1.06</v>
       </c>
       <c r="N66" t="n">
-        <v>1.82</v>
+        <v>2.46</v>
       </c>
       <c r="O66" t="n">
         <v>1.33</v>
       </c>
       <c r="P66" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="R66" t="n">
         <v>1.21</v>
       </c>
       <c r="S66" t="n">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="T66" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U66" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V66" t="n">
         <v>1.11</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G67" t="n">
         <v>2.74</v>
@@ -13376,7 +13376,7 @@
         <v>3.05</v>
       </c>
       <c r="I67" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>3.15</v>
@@ -13427,7 +13427,7 @@
         <v>11</v>
       </c>
       <c r="Z67" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA67" t="n">
         <v>70</v>
@@ -13454,19 +13454,19 @@
         <v>23</v>
       </c>
       <c r="AI67" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ67" t="n">
         <v>48</v>
       </c>
       <c r="AK67" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL67" t="n">
         <v>55</v>
       </c>
       <c r="AM67" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN67" t="n">
         <v>40</v>
@@ -13484,7 +13484,7 @@
         <v>18</v>
       </c>
       <c r="AS67" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT67" t="n">
         <v>7.8</v>
@@ -13496,7 +13496,7 @@
         <v>12.5</v>
       </c>
       <c r="AW67" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX67" t="n">
         <v>14</v>
@@ -13508,29 +13508,29 @@
         <v>17</v>
       </c>
       <c r="BA67" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB67" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC67" t="n">
         <v>5</v>
       </c>
-      <c r="BC67" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD67" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF67" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE67" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF67" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG67" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13561,13 +13561,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G68" t="n">
         <v>3.35</v>
       </c>
       <c r="H68" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I68" t="n">
         <v>2.84</v>
@@ -13579,34 +13579,34 @@
         <v>3.4</v>
       </c>
       <c r="L68" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M68" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N68" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="O68" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P68" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R68" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S68" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T68" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="U68" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V68" t="n">
         <v>1.56</v>
@@ -13615,7 +13615,7 @@
         <v>1.42</v>
       </c>
       <c r="X68" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y68" t="n">
         <v>970</v>
@@ -13630,7 +13630,7 @@
         <v>970</v>
       </c>
       <c r="AC68" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD68" t="n">
         <v>970</v>
@@ -13669,62 +13669,62 @@
         <v>42</v>
       </c>
       <c r="AP68" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ68" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR68" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS68" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AT68" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU68" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AV68" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW68" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AX68" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AY68" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ68" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA68" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BB68" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BC68" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BD68" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="BE68" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="BF68" t="n">
-        <v>6.8</v>
+        <v>2.42</v>
       </c>
       <c r="BG68" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13761,7 +13761,7 @@
         <v>4.5</v>
       </c>
       <c r="H69" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I69" t="n">
         <v>2.72</v>
@@ -13779,16 +13779,16 @@
         <v>1.01</v>
       </c>
       <c r="N69" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O69" t="n">
         <v>1.02</v>
       </c>
       <c r="P69" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R69" t="n">
         <v>1.17</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13973,10 +13973,10 @@
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>1.74</v>
+        <v>2.68</v>
       </c>
       <c r="O70" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P70" t="n">
         <v>1.74</v>
@@ -13985,16 +13985,16 @@
         <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="T70" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U70" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V70" t="n">
         <v>1.35</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
         <v>3.05</v>
       </c>
       <c r="J71" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K71" t="n">
         <v>3.05</v>
@@ -14164,13 +14164,13 @@
         <v>1.62</v>
       </c>
       <c r="M71" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N71" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="O71" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="P71" t="n">
         <v>1.47</v>
@@ -14179,16 +14179,16 @@
         <v>2.88</v>
       </c>
       <c r="R71" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S71" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U71" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="V71" t="n">
         <v>1.48</v>
@@ -14197,116 +14197,116 @@
         <v>1.45</v>
       </c>
       <c r="X71" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y71" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BE71" t="n">
         <v>11</v>
       </c>
-      <c r="Z71" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP71" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ71" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS71" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT71" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU71" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AV71" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW71" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX71" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AY71" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AZ71" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BA71" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB71" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BC71" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD71" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BE71" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BF71" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="BG71" t="n">
-        <v>2.08</v>
+        <v>44</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14337,19 +14337,19 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="G72" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="H72" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I72" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J72" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K72" t="n">
         <v>3.35</v>
@@ -14364,13 +14364,13 @@
         <v>2.74</v>
       </c>
       <c r="O72" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P72" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R72" t="n">
         <v>1.21</v>
@@ -14379,16 +14379,16 @@
         <v>5</v>
       </c>
       <c r="T72" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U72" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V72" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W72" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="X72" t="n">
         <v>11</v>
@@ -14397,7 +14397,7 @@
         <v>970</v>
       </c>
       <c r="Z72" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA72" t="n">
         <v>1000</v>
@@ -14409,10 +14409,10 @@
         <v>970</v>
       </c>
       <c r="AD72" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE72" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AF72" t="n">
         <v>970</v>
@@ -14427,10 +14427,10 @@
         <v>100</v>
       </c>
       <c r="AJ72" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK72" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL72" t="n">
         <v>60</v>
@@ -14445,62 +14445,62 @@
         <v>1000</v>
       </c>
       <c r="AP72" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ72" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR72" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS72" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="AT72" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AU72" t="n">
         <v>6</v>
       </c>
       <c r="AV72" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW72" t="n">
-        <v>2.24</v>
+        <v>2.82</v>
       </c>
       <c r="AX72" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY72" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ72" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA72" t="n">
-        <v>2.24</v>
+        <v>8.6</v>
       </c>
       <c r="BB72" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="BC72" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="BD72" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="BE72" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF72" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BG72" t="n">
-        <v>2.24</v>
+        <v>3.15</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14537,16 +14537,16 @@
         <v>5.2</v>
       </c>
       <c r="H73" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J73" t="n">
         <v>2.62</v>
       </c>
       <c r="K73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14555,31 +14555,31 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P73" t="n">
         <v>1.51</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R73" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S73" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="T73" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U73" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V73" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W73" t="n">
         <v>1.23</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14919,22 +14919,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G75" t="n">
         <v>6.2</v>
       </c>
       <c r="H75" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="I75" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J75" t="n">
         <v>3.35</v>
       </c>
       <c r="K75" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L75" t="n">
         <v>1.01</v>
@@ -14943,7 +14943,7 @@
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O75" t="n">
         <v>1.37</v>
@@ -14952,25 +14952,25 @@
         <v>1.73</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="R75" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S75" t="n">
-        <v>3.4</v>
+        <v>2.24</v>
       </c>
       <c r="T75" t="n">
         <v>1.92</v>
       </c>
       <c r="U75" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V75" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W75" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X75" t="n">
         <v>1000</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G76" t="n">
         <v>2.38</v>
@@ -15122,13 +15122,13 @@
         <v>3.2</v>
       </c>
       <c r="I76" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K76" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L76" t="n">
         <v>1.01</v>
@@ -15137,31 +15137,31 @@
         <v>1.01</v>
       </c>
       <c r="N76" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O76" t="n">
         <v>1.21</v>
       </c>
       <c r="P76" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="R76" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S76" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T76" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U76" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V76" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W76" t="n">
         <v>1.72</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -15307,28 +15307,28 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G77" t="n">
         <v>1.75</v>
       </c>
       <c r="H77" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I77" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J77" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K77" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L77" t="n">
         <v>1.29</v>
       </c>
       <c r="M77" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N77" t="n">
         <v>5</v>
@@ -15343,16 +15343,16 @@
         <v>1.63</v>
       </c>
       <c r="R77" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S77" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="T77" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U77" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V77" t="n">
         <v>1.23</v>
@@ -15367,7 +15367,7 @@
         <v>26</v>
       </c>
       <c r="Z77" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA77" t="n">
         <v>1000</v>
@@ -15376,25 +15376,25 @@
         <v>13</v>
       </c>
       <c r="AC77" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE77" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF77" t="n">
         <v>14</v>
       </c>
       <c r="AG77" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH77" t="n">
         <v>21</v>
       </c>
       <c r="AI77" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ77" t="n">
         <v>21</v>
@@ -15403,28 +15403,28 @@
         <v>19</v>
       </c>
       <c r="AL77" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM77" t="n">
         <v>1000</v>
       </c>
       <c r="AN77" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO77" t="n">
         <v>1000</v>
       </c>
       <c r="AP77" t="n">
-        <v>5.2</v>
+        <v>18.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR77" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS77" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT77" t="n">
         <v>10</v>
@@ -15436,7 +15436,7 @@
         <v>17.5</v>
       </c>
       <c r="AW77" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX77" t="n">
         <v>10.5</v>
@@ -15448,29 +15448,29 @@
         <v>15.5</v>
       </c>
       <c r="BA77" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB77" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC77" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD77" t="n">
         <v>19.5</v>
       </c>
       <c r="BE77" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF77" t="n">
         <v>6.8</v>
       </c>
       <c r="BG77" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
         <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -793,7 +793,7 @@
         <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -805,7 +805,7 @@
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
         <v>1.87</v>
@@ -817,7 +817,7 @@
         <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
         <v>3.85</v>
@@ -981,25 +981,25 @@
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
         <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
         <v>1.52</v>
       </c>
       <c r="U3" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>2.04</v>
@@ -1026,10 +1026,10 @@
         <v>17</v>
       </c>
       <c r="AE3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1038,7 +1038,7 @@
         <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="n">
         <v>24</v>
@@ -1065,10 +1065,10 @@
         <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT3" t="n">
         <v>14</v>
@@ -1080,7 +1080,7 @@
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
         <v>14.5</v>
@@ -1104,7 +1104,7 @@
         <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF3" t="n">
         <v>7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>990</v>
+        <v>1.43</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1193,7 +1193,7 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="W4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1363,13 +1363,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
         <v>2.16</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J6" t="n">
         <v>4.2</v>
@@ -1551,7 +1551,7 @@
         <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
@@ -1569,31 +1569,31 @@
         <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S6" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U6" t="n">
         <v>2.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
         <v>32</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
         <v>26</v>
@@ -1602,10 +1602,10 @@
         <v>26</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
         <v>21</v>
@@ -1632,13 +1632,13 @@
         <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AN6" t="n">
         <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
@@ -1650,7 +1650,7 @@
         <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>19</v>
@@ -1665,7 +1665,7 @@
         <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
@@ -1677,26 +1677,26 @@
         <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
         <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -1757,7 +1757,7 @@
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>1.73</v>
@@ -1769,10 +1769,10 @@
         <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
         <v>2.6</v>
@@ -1838,16 +1838,16 @@
         <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AR7" t="n">
         <v>3.05</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU7" t="n">
         <v>3.3</v>
@@ -1862,13 +1862,13 @@
         <v>4.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
         <v>3.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB7" t="n">
         <v>4.3</v>
@@ -1886,11 +1886,11 @@
         <v>4.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="I8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="J8" t="n">
         <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.3</v>
@@ -1948,10 +1948,10 @@
         <v>5.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q8" t="n">
         <v>1.64</v>
@@ -1960,7 +1960,7 @@
         <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
         <v>1.59</v>
@@ -1969,10 +1969,10 @@
         <v>2.6</v>
       </c>
       <c r="V8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
         <v>21</v>
@@ -1981,10 +1981,10 @@
         <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB8" t="n">
         <v>23</v>
@@ -1999,7 +1999,7 @@
         <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG8" t="n">
         <v>18</v>
@@ -2008,7 +2008,7 @@
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ8" t="n">
         <v>100</v>
@@ -2026,7 +2026,7 @@
         <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP8" t="n">
         <v>18</v>
@@ -2041,50 +2041,50 @@
         <v>15.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW8" t="n">
         <v>15.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AY8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ8" t="n">
         <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
         <v>36</v>
       </c>
       <c r="BC8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE8" t="n">
         <v>29</v>
       </c>
       <c r="BF8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BG8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
         <v>1.54</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
         <v>2.96</v>
@@ -2318,7 +2318,7 @@
         <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
         <v>2.76</v>
@@ -2327,7 +2327,7 @@
         <v>2.92</v>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
         <v>1.16</v>
@@ -2342,10 +2342,10 @@
         <v>1.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
         <v>6.8</v>
@@ -2354,10 +2354,10 @@
         <v>2.32</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
         <v>1.51</v>
@@ -2366,7 +2366,7 @@
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2423,10 +2423,10 @@
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2435,44 +2435,44 @@
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -2506,91 +2506,91 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="J11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.5</v>
       </c>
-      <c r="K11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.48</v>
-      </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF11" t="n">
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
@@ -2608,65 +2608,65 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
         <v>9.199999999999999</v>
@@ -2712,7 +2712,7 @@
         <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2748,7 +2748,7 @@
         <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2805,10 +2805,10 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR12" t="n">
         <v>4.1</v>
@@ -2817,50 +2817,50 @@
         <v>4.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AU12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX12" t="n">
         <v>3.1</v>
       </c>
-      <c r="AV12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AY12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="G13" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
@@ -2924,7 +2924,7 @@
         <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
@@ -2933,19 +2933,19 @@
         <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
         <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
         <v>15.5</v>
@@ -2960,7 +2960,7 @@
         <v>14</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
         <v>16</v>
@@ -2981,7 +2981,7 @@
         <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK13" t="n">
         <v>34</v>
@@ -2993,68 +2993,68 @@
         <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO13" t="n">
         <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>2.62</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11</v>
+        <v>2.56</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>2.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>2.52</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>2.58</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="AX13" t="n">
-        <v>15.5</v>
+        <v>2.7</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>2.52</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>2.64</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>2.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="BF13" t="n">
-        <v>19</v>
+        <v>2.74</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>2.78</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -3085,55 +3085,55 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="J14" t="n">
         <v>2.84</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.64</v>
+        <v>2.56</v>
       </c>
       <c r="O14" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="P14" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
         <v>2.22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V14" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
         <v>1.37</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -3279,67 +3279,67 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="I15" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.36</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.46</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
@@ -3348,7 +3348,7 @@
         <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3384,65 +3384,65 @@
         <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -3721,7 +3721,7 @@
         <v>2.66</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
         <v>26</v>
@@ -3781,10 +3781,10 @@
         <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
@@ -3796,7 +3796,7 @@
         <v>22</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX17" t="n">
         <v>8.199999999999999</v>
@@ -3808,7 +3808,7 @@
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3817,20 +3817,20 @@
         <v>13.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
         <v>6.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G18" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H18" t="n">
         <v>3.35</v>
@@ -3873,10 +3873,10 @@
         <v>3.65</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.37</v>
@@ -3915,10 +3915,10 @@
         <v>1.64</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
         <v>18</v>
@@ -3942,10 +3942,10 @@
         <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3960,7 +3960,7 @@
         <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AR18" t="n">
         <v>17.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="AV18" t="n">
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.9</v>
+        <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF18" t="n">
         <v>16.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.28</v>
@@ -4079,31 +4079,31 @@
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>2.36</v>
       </c>
       <c r="O19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>2.64</v>
+        <v>1.02</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
         <v>1.64</v>
@@ -4124,7 +4124,7 @@
         <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>1.08</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.3</v>
+        <v>1.08</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.7</v>
+        <v>1.08</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>1.08</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.5</v>
+        <v>1.08</v>
       </c>
       <c r="AX19" t="n">
-        <v>4</v>
+        <v>1.08</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.7</v>
+        <v>1.08</v>
       </c>
       <c r="AZ19" t="n">
-        <v>11.5</v>
+        <v>1.08</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.5</v>
+        <v>1.08</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>1.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.5</v>
+        <v>1.08</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.8</v>
+        <v>1.08</v>
       </c>
       <c r="BF19" t="n">
-        <v>10.5</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>1.11</v>
       </c>
       <c r="G20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="H20" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I20" t="n">
         <v>65</v>
       </c>
       <c r="J20" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="K20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="L20" t="n">
         <v>1.24</v>
@@ -4291,16 +4291,16 @@
         <v>2.58</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="X20" t="n">
         <v>26</v>
@@ -4315,7 +4315,7 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>29</v>
@@ -4327,10 +4327,10 @@
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH20" t="n">
         <v>120</v>
@@ -4339,80 +4339,80 @@
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU20" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU20" t="n">
-        <v>17</v>
-      </c>
       <c r="AV20" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -4461,10 +4461,10 @@
         <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
         <v>3.25</v>
@@ -4473,10 +4473,10 @@
         <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
         <v>1.3</v>
@@ -4590,7 +4590,7 @@
         <v>1.41</v>
       </c>
       <c r="BC21" t="n">
-        <v>30</v>
+        <v>1.4</v>
       </c>
       <c r="BD21" t="n">
         <v>1.41</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>1.95</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I22" t="n">
         <v>2.1</v>
@@ -4652,7 +4652,7 @@
         <v>2.1</v>
       </c>
       <c r="K22" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>1.55</v>
       </c>
       <c r="G23" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H23" t="n">
         <v>6.4</v>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
         <v>4.7</v>
@@ -4849,28 +4849,28 @@
         <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P23" t="n">
         <v>2.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R23" t="n">
         <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
         <v>1.76</v>
@@ -4882,7 +4882,7 @@
         <v>1.17</v>
       </c>
       <c r="W23" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X23" t="n">
         <v>24</v>
@@ -4891,10 +4891,10 @@
         <v>28</v>
       </c>
       <c r="Z23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB23" t="n">
         <v>11</v>
@@ -4903,7 +4903,7 @@
         <v>11.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE23" t="n">
         <v>80</v>
@@ -4930,13 +4930,13 @@
         <v>28</v>
       </c>
       <c r="AM23" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
         <v>6.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
         <v>20</v>
@@ -4960,7 +4960,7 @@
         <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX23" t="n">
         <v>9.800000000000001</v>
@@ -4969,7 +4969,7 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA23" t="n">
         <v>11</v>
@@ -4984,17 +4984,17 @@
         <v>24</v>
       </c>
       <c r="BE23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF23" t="n">
         <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G24" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H24" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I24" t="n">
         <v>3.6</v>
@@ -5043,7 +5043,7 @@
         <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
@@ -5055,10 +5055,10 @@
         <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R24" t="n">
         <v>1.54</v>
@@ -5067,7 +5067,7 @@
         <v>2.58</v>
       </c>
       <c r="T24" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U24" t="n">
         <v>2.46</v>
@@ -5076,7 +5076,7 @@
         <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X24" t="n">
         <v>27</v>
@@ -5142,7 +5142,7 @@
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.9</v>
+        <v>48</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -5154,7 +5154,7 @@
         <v>12.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.6</v>
+        <v>29</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G25" t="n">
         <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="J25" t="n">
         <v>3.95</v>
@@ -5267,13 +5267,13 @@
         <v>1.69</v>
       </c>
       <c r="V25" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="W25" t="n">
         <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y25" t="n">
         <v>6.2</v>
@@ -5348,7 +5348,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
         <v>46</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -5416,16 +5416,16 @@
         <v>2.34</v>
       </c>
       <c r="G26" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H26" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I26" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K26" t="n">
         <v>3.4</v>
@@ -5455,16 +5455,16 @@
         <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U26" t="n">
         <v>1.94</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X26" t="n">
         <v>13</v>
@@ -5521,7 +5521,7 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26" t="n">
         <v>8.199999999999999</v>
@@ -5530,16 +5530,16 @@
         <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="AU26" t="n">
         <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="AW26" t="n">
         <v>7</v>
@@ -5548,35 +5548,35 @@
         <v>10.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
         <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC26" t="n">
         <v>7.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="BE26" t="n">
         <v>7.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BG26" t="n">
         <v>7.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>2.16</v>
       </c>
       <c r="I27" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J27" t="n">
         <v>3.7</v>
@@ -5640,7 +5640,7 @@
         <v>2.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R27" t="n">
         <v>1.49</v>
@@ -5676,7 +5676,7 @@
         <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
         <v>970</v>
@@ -5697,7 +5697,7 @@
         <v>32</v>
       </c>
       <c r="AJ27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK27" t="n">
         <v>36</v>
@@ -5709,13 +5709,13 @@
         <v>70</v>
       </c>
       <c r="AN27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO27" t="n">
         <v>970</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ27" t="n">
         <v>9.6</v>
@@ -5724,19 +5724,19 @@
         <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>19</v>
@@ -5748,29 +5748,29 @@
         <v>7</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="BC27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF27" t="n">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG27" t="n">
         <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.9</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
@@ -6058,7 +6058,7 @@
         <v>17</v>
       </c>
       <c r="AA29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
         <v>14</v>
@@ -6082,10 +6082,10 @@
         <v>16.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
         <v>34</v>
@@ -6112,7 +6112,7 @@
         <v>14.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT29" t="n">
         <v>12</v>
@@ -6148,7 +6148,7 @@
         <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29" t="n">
         <v>20</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>3.45</v>
       </c>
       <c r="H30" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I30" t="n">
         <v>2.38</v>
@@ -6207,7 +6207,7 @@
         <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
@@ -6219,7 +6219,7 @@
         <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q30" t="n">
         <v>1.74</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -6383,25 +6383,25 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="G31" t="n">
         <v>4.5</v>
       </c>
       <c r="H31" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="I31" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="J31" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
         <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
@@ -6428,7 +6428,7 @@
         <v>1.89</v>
       </c>
       <c r="U31" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
@@ -6479,58 +6479,58 @@
         <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO31" t="n">
         <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>8.6</v>
+        <v>3.7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="AR31" t="n">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.6</v>
+        <v>3.7</v>
       </c>
       <c r="AW31" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB31" t="n">
         <v>4.9</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD31" t="n">
         <v>4.8</v>
@@ -6542,11 +6542,11 @@
         <v>4.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="G32" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="I32" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="J32" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6601,34 +6601,34 @@
         <v>1.04</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="T32" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6646,7 +6646,7 @@
         <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
         <v>1000</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G33" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H33" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6807,19 +6807,19 @@
         <v>2.26</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S33" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="T33" t="n">
         <v>1.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V33" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W33" t="n">
         <v>1.6</v>
@@ -6828,13 +6828,13 @@
         <v>11</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA33" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB33" t="n">
         <v>9.6</v>
@@ -6843,19 +6843,19 @@
         <v>7.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG33" t="n">
         <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI33" t="n">
         <v>60</v>
@@ -6870,19 +6870,19 @@
         <v>55</v>
       </c>
       <c r="AM33" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO33" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP33" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR33" t="n">
         <v>16.5</v>
@@ -6906,7 +6906,7 @@
         <v>14.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ33" t="n">
         <v>18</v>
@@ -6915,26 +6915,26 @@
         <v>13.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC33" t="n">
         <v>27</v>
       </c>
       <c r="BD33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BF33" t="n">
         <v>27</v>
       </c>
       <c r="BG33" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
         <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M34" t="n">
         <v>1.1</v>
@@ -7016,7 +7016,7 @@
         <v>1.39</v>
       </c>
       <c r="W34" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X34" t="n">
         <v>12.5</v>
@@ -7043,7 +7043,7 @@
         <v>50</v>
       </c>
       <c r="AF34" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG34" t="n">
         <v>12.5</v>
@@ -7082,7 +7082,7 @@
         <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT34" t="n">
         <v>7.4</v>
@@ -7094,7 +7094,7 @@
         <v>12.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX34" t="n">
         <v>12.5</v>
@@ -7106,29 +7106,29 @@
         <v>17</v>
       </c>
       <c r="BA34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC34" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB34" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF34" t="n">
         <v>22</v>
       </c>
       <c r="BG34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -7174,37 +7174,37 @@
         <v>3.35</v>
       </c>
       <c r="K35" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L35" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M35" t="n">
         <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O35" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P35" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S35" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T35" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U35" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V35" t="n">
         <v>1.87</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -7353,58 +7353,58 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N36" t="n">
-        <v>1.38</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
         <v>1.28</v>
       </c>
       <c r="P36" t="n">
-        <v>1.38</v>
+        <v>1.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>1.28</v>
+        <v>2.24</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7419,10 +7419,10 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD36" t="n">
         <v>1000</v>
@@ -7461,62 +7461,62 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="H37" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="I37" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="J37" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="K37" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L37" t="n">
         <v>1.22</v>
@@ -7577,140 +7577,140 @@
         <v>1.15</v>
       </c>
       <c r="P37" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q37" t="n">
         <v>1.46</v>
       </c>
       <c r="R37" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S37" t="n">
         <v>2.12</v>
       </c>
       <c r="T37" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U37" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V37" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="W37" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="X37" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y37" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE37" t="n">
         <v>24</v>
       </c>
-      <c r="AA37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>25</v>
-      </c>
       <c r="AF37" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AG37" t="n">
         <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AI37" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AJ37" t="n">
         <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL37" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AP37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ37" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>12</v>
-      </c>
       <c r="BA37" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
         <v>2.7</v>
       </c>
       <c r="I38" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J38" t="n">
         <v>3.1</v>
@@ -7759,7 +7759,7 @@
         <v>3.35</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M38" t="n">
         <v>1.09</v>
@@ -7783,13 +7783,13 @@
         <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U38" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V38" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W38" t="n">
         <v>1.47</v>
@@ -7882,7 +7882,7 @@
         <v>16</v>
       </c>
       <c r="BA38" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="BB38" t="n">
         <v>7.8</v>
@@ -7891,20 +7891,20 @@
         <v>7.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="BE38" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BF38" t="n">
-        <v>27</v>
+        <v>7.6</v>
       </c>
       <c r="BG38" t="n">
         <v>25</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -7950,10 +7950,10 @@
         <v>2.94</v>
       </c>
       <c r="K39" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
         <v>1.12</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G40" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H40" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I40" t="n">
         <v>3.05</v>
@@ -8144,7 +8144,7 @@
         <v>3.45</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L40" t="n">
         <v>1.32</v>
@@ -8159,7 +8159,7 @@
         <v>1.24</v>
       </c>
       <c r="P40" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q40" t="n">
         <v>1.72</v>
@@ -8198,7 +8198,7 @@
         <v>14.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AD40" t="n">
         <v>13.5</v>
@@ -8246,7 +8246,7 @@
         <v>16</v>
       </c>
       <c r="AS40" t="n">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="AT40" t="n">
         <v>12</v>
@@ -8258,7 +8258,7 @@
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX40" t="n">
         <v>17</v>
@@ -8270,19 +8270,19 @@
         <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BB40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE40" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BF40" t="n">
         <v>13</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G42" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="H42" t="n">
         <v>5</v>
@@ -8535,7 +8535,7 @@
         <v>5.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M42" t="n">
         <v>1.02</v>
@@ -8559,7 +8559,7 @@
         <v>1.92</v>
       </c>
       <c r="T42" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U42" t="n">
         <v>2.58</v>
@@ -8568,7 +8568,7 @@
         <v>1.19</v>
       </c>
       <c r="W42" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="X42" t="n">
         <v>48</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="G43" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H43" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I43" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="J43" t="n">
         <v>4.6</v>
@@ -8729,28 +8729,28 @@
         <v>5</v>
       </c>
       <c r="L43" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
         <v>1.02</v>
       </c>
       <c r="N43" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O43" t="n">
         <v>1.12</v>
       </c>
       <c r="P43" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="R43" t="n">
         <v>1.97</v>
       </c>
       <c r="S43" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="T43" t="n">
         <v>1.43</v>
@@ -8759,10 +8759,10 @@
         <v>2.96</v>
       </c>
       <c r="V43" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X43" t="n">
         <v>55</v>
@@ -8774,7 +8774,7 @@
         <v>22</v>
       </c>
       <c r="AA43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB43" t="n">
         <v>38</v>
@@ -8819,7 +8819,7 @@
         <v>5.8</v>
       </c>
       <c r="AP43" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ43" t="n">
         <v>17</v>
@@ -8864,7 +8864,7 @@
         <v>4.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF43" t="n">
         <v>14</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -8905,16 +8905,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G44" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H44" t="n">
         <v>4.6</v>
       </c>
       <c r="I44" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J44" t="n">
         <v>4.3</v>
@@ -8923,40 +8923,40 @@
         <v>5</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>2.48</v>
+        <v>5.3</v>
       </c>
       <c r="O44" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P44" t="n">
         <v>2.48</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="S44" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="T44" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U44" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V44" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W44" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -8968,7 +8968,7 @@
         <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB44" t="n">
         <v>1000</v>
@@ -9007,68 +9007,68 @@
         <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -9102,13 +9102,13 @@
         <v>2.86</v>
       </c>
       <c r="G45" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H45" t="n">
         <v>2.22</v>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J45" t="n">
         <v>4</v>
@@ -9117,7 +9117,7 @@
         <v>4.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M45" t="n">
         <v>1.02</v>
@@ -9144,13 +9144,13 @@
         <v>1.48</v>
       </c>
       <c r="U45" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="V45" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W45" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="X45" t="n">
         <v>36</v>
@@ -9207,22 +9207,22 @@
         <v>12</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="AQ45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR45" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS45" t="n">
         <v>4.4</v>
       </c>
       <c r="AT45" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU45" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV45" t="n">
         <v>9.4</v>
@@ -9234,7 +9234,7 @@
         <v>19.5</v>
       </c>
       <c r="AY45" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ45" t="n">
         <v>11</v>
@@ -9258,11 +9258,11 @@
         <v>12</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="G46" t="n">
         <v>2.14</v>
@@ -9302,7 +9302,7 @@
         <v>3.35</v>
       </c>
       <c r="I46" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>4</v>
@@ -9317,7 +9317,7 @@
         <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>1.16</v>
@@ -9341,25 +9341,25 @@
         <v>2.66</v>
       </c>
       <c r="V46" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W46" t="n">
         <v>1.87</v>
       </c>
       <c r="X46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y46" t="n">
         <v>26</v>
       </c>
       <c r="Z46" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA46" t="n">
         <v>70</v>
       </c>
       <c r="AB46" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC46" t="n">
         <v>12.5</v>
@@ -9368,7 +9368,7 @@
         <v>18.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF46" t="n">
         <v>20</v>
@@ -9395,34 +9395,34 @@
         <v>60</v>
       </c>
       <c r="AN46" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AO46" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP46" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AQ46" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT46" t="n">
         <v>12</v>
       </c>
       <c r="AU46" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV46" t="n">
         <v>12</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AX46" t="n">
         <v>13</v>
@@ -9434,7 +9434,7 @@
         <v>11.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB46" t="n">
         <v>6.4</v>
@@ -9446,7 +9446,7 @@
         <v>19</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BF46" t="n">
         <v>6.6</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -9490,13 +9490,13 @@
         <v>2.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="H47" t="n">
         <v>2.52</v>
       </c>
       <c r="I47" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="J47" t="n">
         <v>3.8</v>
@@ -9505,16 +9505,16 @@
         <v>4.2</v>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M47" t="n">
         <v>1.03</v>
       </c>
       <c r="N47" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O47" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P47" t="n">
         <v>2.48</v>
@@ -9532,125 +9532,125 @@
         <v>1.51</v>
       </c>
       <c r="U47" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V47" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X47" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Y47" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z47" t="n">
         <v>23</v>
       </c>
-      <c r="Z47" t="n">
-        <v>30</v>
-      </c>
       <c r="AA47" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB47" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AC47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD47" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AE47" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH47" t="n">
         <v>18</v>
       </c>
-      <c r="AE47" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI47" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AJ47" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AK47" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AL47" t="n">
         <v>1000</v>
       </c>
       <c r="AM47" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.95</v>
+        <v>14</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.04</v>
+        <v>6.6</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.84</v>
+        <v>8.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.91</v>
+        <v>10.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="AY47" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2.12</v>
+        <v>12.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BB47" t="n">
-        <v>2.04</v>
+        <v>6.6</v>
       </c>
       <c r="BC47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BD47" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.12</v>
+        <v>10.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>2.12</v>
+        <v>10.5</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
         <v>3.85</v>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>3.7</v>
@@ -9708,7 +9708,7 @@
         <v>4.1</v>
       </c>
       <c r="O48" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P48" t="n">
         <v>2.06</v>
@@ -9729,7 +9729,7 @@
         <v>2.18</v>
       </c>
       <c r="V48" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W48" t="n">
         <v>1.94</v>
@@ -9738,7 +9738,7 @@
         <v>21</v>
       </c>
       <c r="Y48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="n">
         <v>38</v>
@@ -9750,7 +9750,7 @@
         <v>12.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD48" t="n">
         <v>21</v>
@@ -9795,10 +9795,10 @@
         <v>12</v>
       </c>
       <c r="AR48" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS48" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT48" t="n">
         <v>7.6</v>
@@ -9810,7 +9810,7 @@
         <v>12</v>
       </c>
       <c r="AW48" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX48" t="n">
         <v>9.6</v>
@@ -9822,7 +9822,7 @@
         <v>12.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB48" t="n">
         <v>16.5</v>
@@ -9831,20 +9831,20 @@
         <v>14.5</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE48" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF48" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG48" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
         <v>3.15</v>
       </c>
       <c r="G49" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H49" t="n">
         <v>2.46</v>
@@ -9944,7 +9944,7 @@
         <v>12</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD49" t="n">
         <v>12</v>
@@ -9959,7 +9959,7 @@
         <v>14</v>
       </c>
       <c r="AH49" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI49" t="n">
         <v>46</v>
@@ -9986,13 +9986,13 @@
         <v>11</v>
       </c>
       <c r="AQ49" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR49" t="n">
         <v>14</v>
       </c>
       <c r="AS49" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT49" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
         <v>10.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX49" t="n">
         <v>18.5</v>
@@ -10016,29 +10016,29 @@
         <v>15.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC49" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE49" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF49" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG49" t="n">
         <v>19.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -10084,19 +10084,19 @@
         <v>3.45</v>
       </c>
       <c r="K50" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M50" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O50" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P50" t="n">
         <v>1.97</v>
@@ -10111,10 +10111,10 @@
         <v>3.15</v>
       </c>
       <c r="T50" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U50" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V50" t="n">
         <v>1.33</v>
@@ -10123,116 +10123,116 @@
         <v>1.79</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA50" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB50" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF50" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI50" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK50" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM50" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -10263,16 +10263,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I51" t="n">
         <v>3.75</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>4.3</v>
@@ -10314,7 +10314,7 @@
         <v>1.36</v>
       </c>
       <c r="W51" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X51" t="n">
         <v>34</v>
@@ -10332,7 +10332,7 @@
         <v>19</v>
       </c>
       <c r="AC51" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD51" t="n">
         <v>16</v>
@@ -10404,7 +10404,7 @@
         <v>13</v>
       </c>
       <c r="BA51" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB51" t="n">
         <v>24</v>
@@ -10416,17 +10416,17 @@
         <v>20</v>
       </c>
       <c r="BE51" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF51" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG51" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -10457,58 +10457,58 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="G52" t="n">
-        <v>970</v>
+        <v>1.86</v>
       </c>
       <c r="H52" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I52" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="J52" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N52" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R52" t="n">
         <v>1.25</v>
       </c>
-      <c r="O52" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S52" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W52" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10565,62 +10565,62 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -10651,170 +10651,170 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="H53" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="J53" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="K53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X53" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>4.5</v>
       </c>
-      <c r="L53" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BA53" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -10845,170 +10845,170 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="G54" t="n">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="H54" t="n">
         <v>3.1</v>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="K54" t="n">
         <v>3.3</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M54" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N54" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
         <v>1.39</v>
       </c>
       <c r="P54" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="R54" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S54" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="T54" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U54" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="V54" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W54" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="X54" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y54" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA54" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AB54" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF54" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG54" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI54" t="n">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="AJ54" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AK54" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL54" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AM54" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="AN54" t="n">
         <v>32</v>
       </c>
       <c r="AO54" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.41</v>
+        <v>10.5</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.46</v>
+        <v>10</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.38</v>
+        <v>8.6</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.46</v>
+        <v>8.6</v>
       </c>
       <c r="AU54" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="AV54" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>2.52</v>
+        <v>27</v>
       </c>
       <c r="AX54" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY54" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.56</v>
+        <v>11</v>
       </c>
       <c r="BB54" t="n">
-        <v>2.54</v>
+        <v>27</v>
       </c>
       <c r="BC54" t="n">
-        <v>3.1</v>
+        <v>25</v>
       </c>
       <c r="BD54" t="n">
-        <v>2.22</v>
+        <v>12.5</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.46</v>
+        <v>11</v>
       </c>
       <c r="BF54" t="n">
         <v>14.5</v>
       </c>
       <c r="BG54" t="n">
-        <v>3.15</v>
+        <v>24</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -11039,58 +11039,58 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="G55" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="H55" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I55" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="J55" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K55" t="n">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M55" t="n">
         <v>1.02</v>
       </c>
       <c r="N55" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="O55" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P55" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="R55" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="S55" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T55" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U55" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W55" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11141,68 +11141,68 @@
         <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO55" t="n">
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -11236,22 +11236,22 @@
         <v>3.2</v>
       </c>
       <c r="G56" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H56" t="n">
         <v>2.28</v>
       </c>
       <c r="I56" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="J56" t="n">
         <v>3.3</v>
       </c>
       <c r="K56" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L56" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M56" t="n">
         <v>1.07</v>
@@ -11284,7 +11284,7 @@
         <v>1.68</v>
       </c>
       <c r="W56" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X56" t="n">
         <v>16.5</v>
@@ -11326,7 +11326,7 @@
         <v>65</v>
       </c>
       <c r="AK56" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL56" t="n">
         <v>55</v>
@@ -11341,37 +11341,37 @@
         <v>21</v>
       </c>
       <c r="AP56" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="AQ56" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="AR56" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AS56" t="n">
         <v>5.8</v>
       </c>
       <c r="AT56" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="AU56" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AV56" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AW56" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX56" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AY56" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="AZ56" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BA56" t="n">
         <v>6</v>
@@ -11392,11 +11392,11 @@
         <v>6</v>
       </c>
       <c r="BG56" t="n">
-        <v>15</v>
+        <v>5.3</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
         <v>3.35</v>
       </c>
       <c r="T57" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U57" t="n">
         <v>1.97</v>
@@ -11484,34 +11484,34 @@
         <v>17.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z57" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA57" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE57" t="n">
         <v>23</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>24</v>
       </c>
       <c r="AF57" t="n">
         <v>50</v>
       </c>
       <c r="AG57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI57" t="n">
         <v>46</v>
@@ -11532,7 +11532,7 @@
         <v>110</v>
       </c>
       <c r="AO57" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP57" t="n">
         <v>12</v>
@@ -11544,53 +11544,53 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS57" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AV57" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="AX57" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY57" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="AZ57" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BA57" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB57" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BC57" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BD57" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BE57" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF57" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BG57" t="n">
         <v>9</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -11630,13 +11630,13 @@
         <v>3.9</v>
       </c>
       <c r="I58" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K58" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L58" t="n">
         <v>1.58</v>
@@ -11750,7 +11750,7 @@
         <v>15.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AX58" t="n">
         <v>11.5</v>
@@ -11771,7 +11771,7 @@
         <v>28</v>
       </c>
       <c r="BD58" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BE58" t="n">
         <v>46</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G59" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="I59" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="J59" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K59" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L59" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M59" t="n">
         <v>1.07</v>
@@ -11842,19 +11842,19 @@
         <v>3.5</v>
       </c>
       <c r="O59" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P59" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R59" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S59" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="T59" t="n">
         <v>1.96</v>
@@ -11863,46 +11863,46 @@
         <v>1.87</v>
       </c>
       <c r="V59" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="W59" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="X59" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y59" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z59" t="n">
         <v>11</v>
       </c>
       <c r="AA59" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC59" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD59" t="n">
         <v>11.5</v>
       </c>
       <c r="AE59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF59" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG59" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AH59" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI59" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ59" t="n">
         <v>1000</v>
@@ -11911,7 +11911,7 @@
         <v>1000</v>
       </c>
       <c r="AL59" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AM59" t="n">
         <v>1000</v>
@@ -11920,65 +11920,65 @@
         <v>1000</v>
       </c>
       <c r="AO59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP59" t="n">
-        <v>10.5</v>
+        <v>3.85</v>
       </c>
       <c r="AQ59" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="AR59" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="AS59" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="AT59" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="AU59" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="AV59" t="n">
-        <v>7.8</v>
+        <v>3.45</v>
       </c>
       <c r="AW59" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AX59" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC59" t="n">
         <v>4.8</v>
       </c>
-      <c r="AY59" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>5</v>
-      </c>
       <c r="BD59" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE59" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BF59" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG59" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -12012,16 +12012,16 @@
         <v>2.52</v>
       </c>
       <c r="G60" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H60" t="n">
         <v>2.68</v>
       </c>
       <c r="I60" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K60" t="n">
         <v>3.9</v>
@@ -12036,31 +12036,31 @@
         <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P60" t="n">
         <v>1.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="R60" t="n">
         <v>1.25</v>
       </c>
       <c r="S60" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="T60" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U60" t="n">
         <v>1.95</v>
       </c>
       <c r="V60" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W60" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="X60" t="n">
         <v>15</v>
@@ -12090,10 +12090,10 @@
         <v>22</v>
       </c>
       <c r="AG60" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH60" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI60" t="n">
         <v>1000</v>
@@ -12120,25 +12120,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ60" t="n">
-        <v>7.8</v>
+        <v>3.55</v>
       </c>
       <c r="AR60" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="AS60" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AT60" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU60" t="n">
         <v>6.4</v>
       </c>
       <c r="AV60" t="n">
-        <v>8.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW60" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AX60" t="n">
         <v>13</v>
@@ -12147,32 +12147,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ60" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BA60" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BB60" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BC60" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BD60" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BE60" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF60" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BG60" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -12203,13 +12203,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="G61" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H61" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I61" t="n">
         <v>12</v>
@@ -12227,22 +12227,22 @@
         <v>1.04</v>
       </c>
       <c r="N61" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O61" t="n">
         <v>1.24</v>
       </c>
       <c r="P61" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q61" t="n">
         <v>1.72</v>
       </c>
       <c r="R61" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S61" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T61" t="n">
         <v>2.18</v>
@@ -12254,13 +12254,13 @@
         <v>1.09</v>
       </c>
       <c r="W61" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="X61" t="n">
         <v>21</v>
       </c>
       <c r="Y61" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z61" t="n">
         <v>110</v>
@@ -12305,7 +12305,7 @@
         <v>210</v>
       </c>
       <c r="AN61" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO61" t="n">
         <v>270</v>
@@ -12317,13 +12317,13 @@
         <v>25</v>
       </c>
       <c r="AR61" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS61" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT61" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU61" t="n">
         <v>11.5</v>
@@ -12332,16 +12332,16 @@
         <v>28</v>
       </c>
       <c r="AW61" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX61" t="n">
         <v>7</v>
       </c>
       <c r="AY61" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ61" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA61" t="n">
         <v>13</v>
@@ -12356,17 +12356,17 @@
         <v>30</v>
       </c>
       <c r="BE61" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF61" t="n">
         <v>5</v>
       </c>
       <c r="BG61" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -12397,10 +12397,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G62" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H62" t="n">
         <v>5.9</v>
@@ -12409,7 +12409,7 @@
         <v>7.8</v>
       </c>
       <c r="J62" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K62" t="n">
         <v>4.4</v>
@@ -12427,22 +12427,22 @@
         <v>1.33</v>
       </c>
       <c r="P62" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q62" t="n">
         <v>2.08</v>
       </c>
       <c r="R62" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S62" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T62" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V62" t="n">
         <v>1.15</v>
@@ -12451,10 +12451,10 @@
         <v>2.38</v>
       </c>
       <c r="X62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y62" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z62" t="n">
         <v>1000</v>
@@ -12463,7 +12463,7 @@
         <v>230</v>
       </c>
       <c r="AB62" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC62" t="n">
         <v>10.5</v>
@@ -12475,7 +12475,7 @@
         <v>1000</v>
       </c>
       <c r="AF62" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG62" t="n">
         <v>12</v>
@@ -12505,16 +12505,16 @@
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ62" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR62" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS62" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT62" t="n">
         <v>6.8</v>
@@ -12523,10 +12523,10 @@
         <v>8</v>
       </c>
       <c r="AV62" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AW62" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX62" t="n">
         <v>7.4</v>
@@ -12535,32 +12535,32 @@
         <v>4.1</v>
       </c>
       <c r="AZ62" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA62" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB62" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC62" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD62" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE62" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF62" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG62" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G63" t="n">
         <v>2.04</v>
@@ -12600,13 +12600,13 @@
         <v>4</v>
       </c>
       <c r="I63" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>3.8</v>
       </c>
       <c r="K63" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L63" t="n">
         <v>1.37</v>
@@ -12639,7 +12639,7 @@
         <v>2.28</v>
       </c>
       <c r="V63" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W63" t="n">
         <v>1.96</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -12785,170 +12785,170 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="G64" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X64" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA64" t="n">
         <v>4.1</v>
       </c>
-      <c r="H64" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I64" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J64" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K64" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BB64" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -12979,13 +12979,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G65" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H65" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I65" t="n">
         <v>2.22</v>
@@ -13027,25 +13027,25 @@
         <v>2.76</v>
       </c>
       <c r="V65" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W65" t="n">
         <v>1.4</v>
       </c>
       <c r="X65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y65" t="n">
         <v>14.5</v>
       </c>
       <c r="Z65" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA65" t="n">
         <v>28</v>
       </c>
       <c r="AB65" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC65" t="n">
         <v>9.199999999999999</v>
@@ -13057,7 +13057,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG65" t="n">
         <v>14</v>
@@ -13075,7 +13075,7 @@
         <v>32</v>
       </c>
       <c r="AL65" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM65" t="n">
         <v>55</v>
@@ -13084,7 +13084,7 @@
         <v>22</v>
       </c>
       <c r="AO65" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP65" t="n">
         <v>22</v>
@@ -13096,7 +13096,7 @@
         <v>15.5</v>
       </c>
       <c r="AS65" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT65" t="n">
         <v>18.5</v>
@@ -13108,7 +13108,7 @@
         <v>10</v>
       </c>
       <c r="AW65" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX65" t="n">
         <v>26</v>
@@ -13129,10 +13129,10 @@
         <v>29</v>
       </c>
       <c r="BD65" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE65" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF65" t="n">
         <v>20</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -13176,16 +13176,16 @@
         <v>1.72</v>
       </c>
       <c r="G66" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H66" t="n">
         <v>5.4</v>
       </c>
       <c r="I66" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J66" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K66" t="n">
         <v>4.1</v>
@@ -13197,13 +13197,13 @@
         <v>1.07</v>
       </c>
       <c r="N66" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O66" t="n">
         <v>1.34</v>
       </c>
       <c r="P66" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q66" t="n">
         <v>2</v>
@@ -13212,7 +13212,7 @@
         <v>1.33</v>
       </c>
       <c r="S66" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T66" t="n">
         <v>1.92</v>
@@ -13287,19 +13287,19 @@
         <v>15.5</v>
       </c>
       <c r="AR66" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS66" t="n">
         <v>11</v>
       </c>
       <c r="AT66" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU66" t="n">
         <v>7.6</v>
       </c>
       <c r="AV66" t="n">
-        <v>19</v>
+        <v>7.6</v>
       </c>
       <c r="AW66" t="n">
         <v>10.5</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -13373,7 +13373,7 @@
         <v>1.7</v>
       </c>
       <c r="H67" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I67" t="n">
         <v>9.6</v>
@@ -13388,40 +13388,40 @@
         <v>1.01</v>
       </c>
       <c r="M67" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N67" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O67" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="R67" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="S67" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="T67" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U67" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="V67" t="n">
         <v>1.11</v>
       </c>
       <c r="W67" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X67" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y67" t="n">
         <v>1000</v>
@@ -13433,31 +13433,31 @@
         <v>1000</v>
       </c>
       <c r="AB67" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC67" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD67" t="n">
         <v>1000</v>
       </c>
       <c r="AE67" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF67" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG67" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH67" t="n">
         <v>1000</v>
       </c>
       <c r="AI67" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK67" t="n">
         <v>1000</v>
@@ -13466,71 +13466,71 @@
         <v>1000</v>
       </c>
       <c r="AM67" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN67" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO67" t="n">
         <v>1000</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU67" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV67" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW67" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY67" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA67" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD67" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE67" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF67" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG67" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G68" t="n">
         <v>2.72</v>
@@ -13570,7 +13570,7 @@
         <v>3.1</v>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J68" t="n">
         <v>3.15</v>
@@ -13588,10 +13588,10 @@
         <v>2.94</v>
       </c>
       <c r="O68" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P68" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q68" t="n">
         <v>2.3</v>
@@ -13606,7 +13606,7 @@
         <v>1.93</v>
       </c>
       <c r="U68" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V68" t="n">
         <v>1.42</v>
@@ -13690,7 +13690,7 @@
         <v>12.5</v>
       </c>
       <c r="AW68" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX68" t="n">
         <v>14</v>
@@ -13705,26 +13705,26 @@
         <v>5.5</v>
       </c>
       <c r="BB68" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC68" t="n">
         <v>5.1</v>
       </c>
       <c r="BD68" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE68" t="n">
         <v>5.7</v>
       </c>
       <c r="BF68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG68" t="n">
         <v>5.4</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -13758,22 +13758,22 @@
         <v>3.05</v>
       </c>
       <c r="G69" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H69" t="n">
         <v>2.56</v>
       </c>
       <c r="I69" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J69" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="K69" t="n">
         <v>3.35</v>
       </c>
       <c r="L69" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M69" t="n">
         <v>1.11</v>
@@ -13797,10 +13797,10 @@
         <v>4.7</v>
       </c>
       <c r="T69" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U69" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="V69" t="n">
         <v>1.56</v>
@@ -13824,7 +13824,7 @@
         <v>970</v>
       </c>
       <c r="AC69" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AD69" t="n">
         <v>970</v>
@@ -13863,7 +13863,7 @@
         <v>42</v>
       </c>
       <c r="AP69" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ69" t="n">
         <v>4.3</v>
@@ -13872,19 +13872,19 @@
         <v>5.6</v>
       </c>
       <c r="AS69" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT69" t="n">
         <v>4.6</v>
       </c>
       <c r="AU69" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AV69" t="n">
         <v>5.1</v>
       </c>
       <c r="AW69" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="AX69" t="n">
         <v>6</v>
@@ -13893,32 +13893,32 @@
         <v>5.3</v>
       </c>
       <c r="AZ69" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA69" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="BB69" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="BC69" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="BD69" t="n">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="BE69" t="n">
-        <v>2.18</v>
+        <v>3.25</v>
       </c>
       <c r="BF69" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="BG69" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -13952,16 +13952,16 @@
         <v>3.45</v>
       </c>
       <c r="G70" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H70" t="n">
         <v>2.22</v>
       </c>
       <c r="I70" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="J70" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
         <v>3.5</v>
@@ -13970,58 +13970,58 @@
         <v>1.01</v>
       </c>
       <c r="M70" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N70" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="O70" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="P70" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R70" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S70" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T70" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U70" t="n">
         <v>1.84</v>
       </c>
-      <c r="U70" t="n">
-        <v>1.68</v>
-      </c>
       <c r="V70" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W70" t="n">
         <v>1.32</v>
       </c>
       <c r="X70" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y70" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z70" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA70" t="n">
         <v>1000</v>
       </c>
       <c r="AB70" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC70" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD70" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE70" t="n">
         <v>1000</v>
@@ -14057,62 +14057,62 @@
         <v>1000</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU70" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV70" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW70" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX70" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AY70" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ70" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA70" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB70" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC70" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD70" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE70" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF70" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG70" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -14143,170 +14143,170 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G71" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="H71" t="n">
         <v>3.05</v>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="J71" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K71" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N71" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S71" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X71" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT71" t="n">
         <v>3.6</v>
       </c>
-      <c r="L71" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N71" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P71" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>2</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S71" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V71" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W71" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP71" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ71" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS71" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT71" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AU71" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV71" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AW71" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX71" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY71" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ71" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA71" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB71" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC71" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD71" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE71" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF71" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG71" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -14337,19 +14337,19 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G72" t="n">
         <v>3.25</v>
       </c>
       <c r="H72" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J72" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="K72" t="n">
         <v>3.1</v>
@@ -14367,16 +14367,16 @@
         <v>1.63</v>
       </c>
       <c r="P72" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.63</v>
+        <v>2.88</v>
       </c>
       <c r="R72" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S72" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T72" t="n">
         <v>2.2</v>
@@ -14391,37 +14391,37 @@
         <v>1.45</v>
       </c>
       <c r="X72" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y72" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z72" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA72" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB72" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC72" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD72" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE72" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF72" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG72" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH72" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI72" t="n">
         <v>1000</v>
@@ -14430,13 +14430,13 @@
         <v>1000</v>
       </c>
       <c r="AK72" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL72" t="n">
         <v>1000</v>
       </c>
       <c r="AM72" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN72" t="n">
         <v>1000</v>
@@ -14445,62 +14445,62 @@
         <v>1000</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AQ72" t="n">
         <v>7</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT72" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU72" t="n">
         <v>6.2</v>
       </c>
       <c r="AV72" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW72" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX72" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY72" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ72" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA72" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB72" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC72" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD72" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE72" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF72" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG72" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
         <v>3.35</v>
       </c>
       <c r="L73" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M73" t="n">
         <v>1.12</v>
@@ -14579,7 +14579,7 @@
         <v>1.81</v>
       </c>
       <c r="V73" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W73" t="n">
         <v>1.8</v>
@@ -14597,7 +14597,7 @@
         <v>1000</v>
       </c>
       <c r="AB73" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC73" t="n">
         <v>970</v>
@@ -14612,7 +14612,7 @@
         <v>970</v>
       </c>
       <c r="AG73" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH73" t="n">
         <v>23</v>
@@ -14639,62 +14639,62 @@
         <v>1000</v>
       </c>
       <c r="AP73" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AR73" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS73" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD73" t="n">
         <v>3.5</v>
       </c>
-      <c r="AT73" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU73" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV73" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW73" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AX73" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY73" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ73" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA73" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB73" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC73" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD73" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE73" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF73" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG73" t="n">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -14725,58 +14725,58 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="G74" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H74" t="n">
         <v>1.9</v>
       </c>
       <c r="I74" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="J74" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K74" t="n">
-        <v>5.7</v>
+        <v>3.95</v>
       </c>
       <c r="L74" t="n">
         <v>1.01</v>
       </c>
       <c r="M74" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N74" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="O74" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P74" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R74" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T74" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U74" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="V74" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="W74" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X74" t="n">
         <v>1000</v>
@@ -14833,62 +14833,62 @@
         <v>1000</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT74" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU74" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="AV74" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW74" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX74" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY74" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ74" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BA74" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB74" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC74" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD74" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE74" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF74" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG74" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -14943,16 +14943,16 @@
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="O75" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P75" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R75" t="n">
         <v>1.18</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -15113,64 +15113,64 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="G76" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H76" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="I76" t="n">
         <v>2.04</v>
       </c>
       <c r="J76" t="n">
-        <v>3.35</v>
+        <v>1.19</v>
       </c>
       <c r="K76" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L76" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M76" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N76" t="n">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="O76" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P76" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="S76" t="n">
-        <v>3.55</v>
+        <v>2.24</v>
       </c>
       <c r="T76" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U76" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="V76" t="n">
         <v>1.97</v>
       </c>
       <c r="W76" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X76" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y76" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z76" t="n">
         <v>1000</v>
@@ -15179,13 +15179,13 @@
         <v>1000</v>
       </c>
       <c r="AB76" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC76" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD76" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE76" t="n">
         <v>1000</v>
@@ -15194,7 +15194,7 @@
         <v>1000</v>
       </c>
       <c r="AG76" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH76" t="n">
         <v>1000</v>
@@ -15221,62 +15221,62 @@
         <v>1000</v>
       </c>
       <c r="AP76" t="n">
-        <v>8.6</v>
+        <v>1.7</v>
       </c>
       <c r="AQ76" t="n">
-        <v>5.7</v>
+        <v>1.46</v>
       </c>
       <c r="AR76" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AS76" t="n">
-        <v>3.65</v>
+        <v>1.61</v>
       </c>
       <c r="AT76" t="n">
-        <v>10.5</v>
+        <v>1.56</v>
       </c>
       <c r="AU76" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AV76" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="AW76" t="n">
-        <v>3.65</v>
+        <v>1.7</v>
       </c>
       <c r="AX76" t="n">
-        <v>3.85</v>
+        <v>1.7</v>
       </c>
       <c r="AY76" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="AZ76" t="n">
-        <v>3.6</v>
+        <v>1.61</v>
       </c>
       <c r="BA76" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="BB76" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="BC76" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="BD76" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="BE76" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="BF76" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="BG76" t="n">
-        <v>12</v>
+        <v>1.7</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -15307,170 +15307,170 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G77" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="H77" t="n">
         <v>3.2</v>
       </c>
       <c r="I77" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="J77" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="K77" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L77" t="n">
         <v>1.01</v>
       </c>
       <c r="M77" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N77" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="O77" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P77" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="R77" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S77" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="T77" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="U77" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V77" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W77" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="X77" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y77" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z77" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA77" t="n">
         <v>1000</v>
       </c>
       <c r="AB77" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC77" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD77" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE77" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF77" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG77" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH77" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI77" t="n">
         <v>1000</v>
       </c>
       <c r="AJ77" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK77" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL77" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM77" t="n">
         <v>1000</v>
       </c>
       <c r="AN77" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO77" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT77" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU77" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV77" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW77" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX77" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY77" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ77" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA77" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB77" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC77" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD77" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE77" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF77" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG77" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>
@@ -15525,7 +15525,7 @@
         <v>1.04</v>
       </c>
       <c r="N78" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O78" t="n">
         <v>1.21</v>
@@ -15540,10 +15540,10 @@
         <v>1.57</v>
       </c>
       <c r="S78" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T78" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U78" t="n">
         <v>2.28</v>
@@ -15615,7 +15615,7 @@
         <v>6.2</v>
       </c>
       <c r="AR78" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS78" t="n">
         <v>7.4</v>
@@ -15630,7 +15630,7 @@
         <v>17.5</v>
       </c>
       <c r="AW78" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX78" t="n">
         <v>10.5</v>
@@ -15648,7 +15648,7 @@
         <v>15.5</v>
       </c>
       <c r="BC78" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD78" t="n">
         <v>19.5</v>
@@ -15660,11 +15660,11 @@
         <v>6.8</v>
       </c>
       <c r="BG78" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-19 06:19:43</t>
+          <t>2026-03-19 08:39:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.8</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
-        <v>8.4</v>
+        <v>1.25</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79</v>
+        <v>32</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -781,43 +781,43 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.06</v>
+        <v>2.9</v>
       </c>
       <c r="S2" t="n">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -826,108 +826,108 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AL2" t="n">
         <v>11</v>
       </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.52</v>
+        <v>15</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="AV2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>2.86</v>
       </c>
       <c r="AZ2" t="n">
-        <v>40</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>44</v>
+        <v>3.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="BF2" t="n">
-        <v>48</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>110</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28</v>
+        <v>1.51</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="AD3" t="n">
         <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>430</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>320</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG3" t="n">
         <v>150</v>
       </c>
-      <c r="AN3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>42</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
@@ -1136,186 +1136,186 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>1.28</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>1.29</v>
       </c>
       <c r="H4" t="n">
-        <v>2.84</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>2.88</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.15</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.64</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.74</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>4.4</v>
       </c>
       <c r="X4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY4" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="BB4" t="n">
-        <v>50</v>
+        <v>10.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BE4" t="n">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="BF4" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="BG4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atl Tucuman</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>1.51</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
         <v>5.5</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AI5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM5" t="n">
         <v>27</v>
       </c>
-      <c r="AA5" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>220</v>
-      </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>5.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="BE5" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="BF5" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BG5" t="n">
-        <v>55</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,100 +1524,100 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Atletico Choloma</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.26</v>
+        <v>800</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>800</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>7.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>1.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.81</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3</v>
+        <v>1.12</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.9</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1635,75 +1635,75 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.6</v>
+        <v>1.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>1.05</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>1.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>1.05</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>1.05</v>
       </c>
       <c r="AX6" t="n">
-        <v>20</v>
+        <v>1.05</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>1.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17</v>
+        <v>1.05</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>1.05</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>1.05</v>
       </c>
       <c r="BC6" t="n">
-        <v>36</v>
+        <v>1.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="BF6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>1.05</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atletico Choloma</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>5.8</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.92</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="X7" t="n">
-        <v>48</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL7" t="n">
         <v>42</v>
       </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.75</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.95</v>
+        <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.55</v>
+        <v>44</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.3</v>
+        <v>26</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.5</v>
+        <v>85</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.95</v>
+        <v>34</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Australian A-League Men</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,378 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Auckland FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Macarthur FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="X8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB8" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF8" t="n">
+      <c r="BC8" t="n">
         <v>15</v>
       </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI8" t="n">
+      <c r="BD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>46</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>29</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-20 19:44:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Australian A-League Men</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Auckland FC</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Macarthur FC</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-03-20 19:44:28</t>
+          <t>2026-03-20 22:15:59</t>
         </is>
       </c>
     </row>
